--- a/tpe_study/results/tables/all_results.xlsx
+++ b/tpe_study/results/tables/all_results.xlsx
@@ -520,7 +520,7 @@
         <v>0.001</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -532,22 +532,22 @@
         <v/>
       </c>
       <c r="J2" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4396179471017895</v>
+        <v>0.5564342229857804</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2396293491454449</v>
+        <v>0.2990910379555807</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3049693078620062</v>
+        <v>0.3459776243185908</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.5468025656662376</v>
       </c>
     </row>
     <row r="3">
@@ -575,34 +575,34 @@
         <v>0.001</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>47.5</v>
+        <v>47.1304347826087</v>
       </c>
       <c r="I3" t="n">
-        <v>15.07481343168134</v>
+        <v>14.04744862437455</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3132837736807098</v>
+        <v>0.208474810355531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0027488008240664</v>
+        <v>0.0023012376044553</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1819528125953422</v>
+        <v>0.1482805504521079</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2800961527976047</v>
+        <v>0.2176688680596704</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0524283970379772</v>
+        <v>0.0479691197213039</v>
       </c>
     </row>
     <row r="4">
@@ -630,34 +630,34 @@
         <v>0.001</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>34.125</v>
+        <v>45.94444444444444</v>
       </c>
       <c r="I4" t="n">
-        <v>11.73070223814414</v>
+        <v>18.95161154748888</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0478868897788192</v>
+        <v>0.033462798467233</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1072454602027986</v>
+        <v>0.0947984085744001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0021386608451633</v>
+        <v>0.0022110711933337</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1275887324970493</v>
+        <v>0.105255345479735</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1777864030757573</v>
+        <v>0.1496132036792697</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0462408203953976</v>
+        <v>0.0470218949143926</v>
       </c>
     </row>
     <row r="5">
@@ -685,34 +685,34 @@
         <v>0.001</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H5" t="n">
-        <v>39</v>
+        <v>40.6595744680851</v>
       </c>
       <c r="I5" t="n">
-        <v>15.17962623491036</v>
+        <v>15.68476235177596</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001576889925524</v>
+        <v>0.001039217390027</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002563686755872</v>
+        <v>0.0045886698625276</v>
       </c>
       <c r="L5" t="n">
-        <v>6.561325648454233e-05</v>
+        <v>7.12412432760333e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0100554104722364</v>
+        <v>0.0154768037567931</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0075218157905743</v>
+        <v>0.028278718774032</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008098352863641099</v>
+        <v>0.0084387922964341</v>
       </c>
     </row>
     <row r="6">
@@ -740,34 +740,34 @@
         <v>0.001</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
         <v>90</v>
       </c>
       <c r="H6" t="n">
-        <v>33.83333333333334</v>
+        <v>35.02222222222223</v>
       </c>
       <c r="I6" t="n">
-        <v>12.51332622979731</v>
+        <v>12.31347751023494</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003188894368445</v>
+        <v>0.0029001126302991</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0007330744420781</v>
+        <v>0.015133676406169</v>
       </c>
       <c r="L6" t="n">
-        <v>4.841637741950355e-05</v>
+        <v>4.870698555282918e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0123342490641131</v>
+        <v>0.019283522202299</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0129133937006898</v>
+        <v>0.0502817899618997</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0069579950293813</v>
+        <v>0.0069789709711874</v>
       </c>
     </row>
     <row r="7">
@@ -795,34 +795,34 @@
         <v>0.001</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v/>
+        <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v/>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0171162409542543</v>
+        <v>0.045029390867651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.018055034587628</v>
+        <v>0.0202014290924368</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1467344656676207</v>
+        <v>0.1559023321461803</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0574830408800592</v>
+        <v>0.0897810365861131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1341481696768977</v>
+        <v>0.1421314508741648</v>
       </c>
     </row>
     <row r="8">
@@ -850,7 +850,7 @@
         <v>0.001</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -862,22 +862,22 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4396179471017895</v>
+        <v>0.5564342229857804</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2396293491454449</v>
+        <v>0.2990910379555807</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3049693078620062</v>
+        <v>0.3459776243185908</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.5468025656662376</v>
       </c>
     </row>
     <row r="9">
@@ -905,34 +905,34 @@
         <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>45.16666666666666</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="I9" t="n">
-        <v>17.43001880537011</v>
+        <v>14.2214322396901</v>
       </c>
       <c r="J9" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2687732919211391</v>
+        <v>0.1792683205090033</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0049896483329344</v>
+        <v>0.0052306036749893</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1998309745729286</v>
+        <v>0.1621836264902457</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2634586283614347</v>
+        <v>0.196434230846899</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07058653651715679</v>
+        <v>0.07231665780340819</v>
       </c>
     </row>
     <row r="10">
@@ -960,34 +960,34 @@
         <v>0.001</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>43.42857142857143</v>
+        <v>47.23076923076923</v>
       </c>
       <c r="I10" t="n">
-        <v>23.59695587423539</v>
+        <v>23.33750314953246</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0776696659269543</v>
+        <v>0.0435392673013738</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1554857836003083</v>
+        <v>0.1140306250017365</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0067698752173749</v>
+        <v>0.0042424807016868</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1715122576387288</v>
+        <v>0.1261698481298532</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2196661362309189</v>
+        <v>0.1661939731887519</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0792835014218506</v>
+        <v>0.06512597316304421</v>
       </c>
     </row>
     <row r="11">
@@ -1015,34 +1015,34 @@
         <v>0.001</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
-        <v>40.33333333333334</v>
+        <v>40.87878787878788</v>
       </c>
       <c r="I11" t="n">
-        <v>18.10586154321915</v>
+        <v>16.56896985835649</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001454395450638</v>
+        <v>0.0022785422918566</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0012911989296875</v>
+        <v>0.002965280813584</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009559333821756</v>
+        <v>0.0013390103216118</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0347527523747741</v>
+        <v>0.0417805044648733</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0157048289712324</v>
+        <v>0.0230853143473803</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0309180858483409</v>
+        <v>0.0365924734661286</v>
       </c>
     </row>
     <row r="12">
@@ -1070,34 +1070,34 @@
         <v>0.001</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H12" t="n">
-        <v>33.44444444444444</v>
+        <v>36.57575757575758</v>
       </c>
       <c r="I12" t="n">
-        <v>15.29060067936516</v>
+        <v>16.72601005335304</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0019264161245788</v>
+        <v>0.0015910837231041</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0013840420932628</v>
+        <v>0.0016679273857029</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0016978536843013</v>
+        <v>0.0010252476847121</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0403912926622152</v>
+        <v>0.0343422322692095</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0171743879557363</v>
+        <v>0.0202902638196698</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0412014573486585</v>
+        <v>0.032019066741684</v>
       </c>
     </row>
     <row r="13">
@@ -1125,34 +1125,34 @@
         <v>0.001</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v/>
+        <v>56</v>
       </c>
       <c r="I13" t="n">
-        <v/>
+        <v>16.67333200053307</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0195287817162793</v>
+        <v>0.0494374024141801</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0181084334492233</v>
+        <v>0.0204762031369927</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1542279335364008</v>
+        <v>0.1632645918866416</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0581396090092027</v>
+        <v>0.0963443465750241</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1345223032287276</v>
+        <v>0.1430897055927048</v>
       </c>
     </row>
     <row r="14">
@@ -1180,7 +1180,7 @@
         <v>0.001</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1192,22 +1192,22 @@
         <v/>
       </c>
       <c r="J14" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4396179471017895</v>
+        <v>0.5564342229857804</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2396293491454449</v>
+        <v>0.2990910379555807</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3049693078620062</v>
+        <v>0.3459776243185908</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.5468025656662376</v>
       </c>
     </row>
     <row r="15">
@@ -1235,34 +1235,34 @@
         <v>0.001</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" t="n">
-        <v>47.5</v>
+        <v>47.1304347826087</v>
       </c>
       <c r="I15" t="n">
-        <v>15.07481343168134</v>
+        <v>14.04744862437455</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3132837736807098</v>
+        <v>0.208474810355531</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0027488008240664</v>
+        <v>0.0023012376044553</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1819528125953422</v>
+        <v>0.1482805504521079</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2800961527976047</v>
+        <v>0.2176688680596704</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0524283970379772</v>
+        <v>0.0479691197213039</v>
       </c>
     </row>
     <row r="16">
@@ -1290,34 +1290,34 @@
         <v>0.001</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H16" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>12.72792206135786</v>
+        <v>16.76305461424021</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1027591027792983</v>
+        <v>0.07026897685516401</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1862884631272388</v>
+        <v>0.1452622186233921</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0023887032738445</v>
+        <v>0.001136550458681</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1890853437052657</v>
+        <v>0.1518954126704325</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2588548542623063</v>
+        <v>0.2172481541114747</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0474178031094615</v>
+        <v>0.0336582383257454</v>
       </c>
     </row>
     <row r="17">
@@ -1345,34 +1345,34 @@
         <v>0.001</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>53.125</v>
+        <v>49.64</v>
       </c>
       <c r="I17" t="n">
-        <v>15.89368978557213</v>
+        <v>14.5103549232953</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0278407789078835</v>
+        <v>0.0244986007715494</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0546393550781141</v>
+        <v>0.0495728598560394</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0042123610885516</v>
+        <v>0.0015400750213268</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1071950788665455</v>
+        <v>0.0970406891100932</v>
       </c>
       <c r="N17" t="n">
-        <v>0.127867094964571</v>
+        <v>0.1228075951583927</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0647825964620103</v>
+        <v>0.0383329457982301</v>
       </c>
     </row>
     <row r="18">
@@ -1400,34 +1400,34 @@
         <v>0.001</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H18" t="n">
-        <v>47.44444444444444</v>
+        <v>43.34782608695652</v>
       </c>
       <c r="I18" t="n">
-        <v>17.09523072614836</v>
+        <v>15.64444253499062</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0739482796561807</v>
+        <v>0.0653989089806865</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1468621297527787</v>
+        <v>0.1508248703375531</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001688608279338</v>
+        <v>0.0022912811635599</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1526880764144908</v>
+        <v>0.1486103911817424</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2250214011533643</v>
+        <v>0.2081198227307912</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0407637545766886</v>
+        <v>0.0478304808575516</v>
       </c>
     </row>
     <row r="19">
@@ -1455,34 +1455,34 @@
         <v>0.001</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v/>
+        <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v/>
+        <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0171162409542543</v>
+        <v>0.045029390867651</v>
       </c>
       <c r="L19" t="n">
-        <v>0.018055034587628</v>
+        <v>0.0202014290924368</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1467344656676207</v>
+        <v>0.1559023321461803</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0574830408800592</v>
+        <v>0.0897810365861131</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1341481696768977</v>
+        <v>0.1421314508741648</v>
       </c>
     </row>
     <row r="20">
@@ -1510,7 +1510,7 @@
         <v>0.001</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1522,22 +1522,22 @@
         <v/>
       </c>
       <c r="J20" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4396179471017895</v>
+        <v>0.5564342229857804</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2396293491454449</v>
+        <v>0.2990910379555807</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3049693078620062</v>
+        <v>0.3459776243185908</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.5468025656662376</v>
       </c>
     </row>
     <row r="21">
@@ -1565,34 +1565,34 @@
         <v>0.001</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H21" t="n">
-        <v>45.16666666666666</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="I21" t="n">
-        <v>17.43001880537011</v>
+        <v>14.2214322396901</v>
       </c>
       <c r="J21" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2687732919211391</v>
+        <v>0.1792683205090033</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0049896483329344</v>
+        <v>0.0052306036749893</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1998309745729286</v>
+        <v>0.1621836264902457</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2634586283614347</v>
+        <v>0.196434230846899</v>
       </c>
       <c r="O21" t="n">
-        <v>0.07058653651715679</v>
+        <v>0.07231665780340819</v>
       </c>
     </row>
     <row r="22">
@@ -1620,34 +1620,34 @@
         <v>0.001</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H22" t="n">
-        <v>56.66666666666666</v>
+        <v>50.125</v>
       </c>
       <c r="I22" t="n">
-        <v>10.24152766382481</v>
+        <v>17.57439543768149</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0945757989443753</v>
+        <v>0.0596004780297778</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1662501855395396</v>
+        <v>0.1268668924962294</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0087181941189441</v>
+        <v>0.0045461572808414</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2069335216821159</v>
+        <v>0.1561473070809447</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2274957506166051</v>
+        <v>0.1876659173135789</v>
       </c>
       <c r="O22" t="n">
-        <v>0.092728811368063</v>
+        <v>0.06740304487325489</v>
       </c>
     </row>
     <row r="23">
@@ -1675,34 +1675,34 @@
         <v>0.001</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H23" t="n">
-        <v>54.28571428571428</v>
+        <v>49.58823529411764</v>
       </c>
       <c r="I23" t="n">
-        <v>17.21887905522213</v>
+        <v>18.85879050307189</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0272042912092492</v>
+        <v>0.023288155223405</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07079703825688829</v>
+        <v>0.0525236398115302</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0040539393711476</v>
+        <v>0.0051271610495102</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1014106099207696</v>
+        <v>0.1034520815299974</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1300775899405687</v>
+        <v>0.1121865502211198</v>
       </c>
       <c r="O23" t="n">
-        <v>0.063519309930975</v>
+        <v>0.0715132406625681</v>
       </c>
     </row>
     <row r="24">
@@ -1730,34 +1730,34 @@
         <v>0.001</v>
       </c>
       <c r="F24" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" t="n">
         <v>20</v>
       </c>
-      <c r="G24" t="n">
-        <v>15</v>
-      </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I24" t="n">
-        <v>9.626352718795768</v>
+        <v>15.97498043817269</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0647658539144659</v>
+        <v>0.06591725041837081</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1186432200590779</v>
+        <v>0.1480488544594876</v>
       </c>
       <c r="L24" t="n">
-        <v>0.008080698083592099</v>
+        <v>0.007574895200093</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1731680580449073</v>
+        <v>0.1711803626946721</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1864904222404506</v>
+        <v>0.1913492457421542</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0897914792339826</v>
+        <v>0.0870210442131016</v>
       </c>
     </row>
     <row r="25">
@@ -1785,34 +1785,34 @@
         <v>0.001</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v/>
+        <v>56</v>
       </c>
       <c r="I25" t="n">
-        <v/>
+        <v>16.67333200053307</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0195287817162793</v>
+        <v>0.0494374024141801</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0181084334492233</v>
+        <v>0.0204762031369927</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1542279335364008</v>
+        <v>0.1632645918866416</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0581396090092027</v>
+        <v>0.0963443465750241</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1345223032287276</v>
+        <v>0.1430897055927048</v>
       </c>
     </row>
     <row r="26">
@@ -1840,34 +1840,34 @@
         <v>0.05</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="I26" t="n">
-        <v>9.41629792788369</v>
+        <v>10.66958293467931</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8210335882833985</v>
+        <v>0.846870767044112</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3999705958906486</v>
+        <v>0.5391841538320152</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.845471059700435</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5808794108782485</v>
+        <v>0.5613417921707943</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7268581750621723</v>
+        <v>0.819333745326341</v>
       </c>
     </row>
     <row r="27">
@@ -1895,34 +1895,34 @@
         <v>0.05</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>23.11565126344775</v>
       </c>
       <c r="J27" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="K27" t="n">
-        <v>2.143521731111417</v>
+        <v>1.823052405821786</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5618029682163718</v>
+        <v>0.4436778167400766</v>
       </c>
       <c r="M27" t="n">
-        <v>1.444186909187633</v>
+        <v>1.257662594961341</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7190814750073178</v>
+        <v>0.6942617144916274</v>
       </c>
       <c r="O27" t="n">
-        <v>1.391545000285481</v>
+        <v>1.183199506670446</v>
       </c>
     </row>
     <row r="28">
@@ -1950,34 +1950,34 @@
         <v>0.05</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
-      </c>
       <c r="J28" t="n">
-        <v>1.026560398956106</v>
+        <v>0.7843253210412064</v>
       </c>
       <c r="K28" t="n">
-        <v>1.783103781401299</v>
+        <v>1.237199282463882</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4296638193202227</v>
+        <v>0.410608784284006</v>
       </c>
       <c r="M28" t="n">
-        <v>0.979619593345628</v>
+        <v>0.8966171596061158</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4901034142114751</v>
+        <v>0.4635877730223712</v>
       </c>
       <c r="O28" t="n">
-        <v>0.976272180573054</v>
+        <v>0.8736859045127042</v>
       </c>
     </row>
     <row r="29">
@@ -2005,34 +2005,34 @@
         <v>0.05</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H29" t="n">
-        <v>25.75</v>
+        <v>29.88235294117647</v>
       </c>
       <c r="I29" t="n">
-        <v>8.968695557326049</v>
+        <v>15.04066000171526</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5430921795874392</v>
+        <v>0.3778103600790315</v>
       </c>
       <c r="K29" t="n">
-        <v>1.532437287575102</v>
+        <v>1.006856595115819</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1130634684010599</v>
+        <v>0.156418444876398</v>
       </c>
       <c r="M29" t="n">
-        <v>0.751396205677789</v>
+        <v>0.8283534722804042</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8241367479234829</v>
+        <v>0.684659532300132</v>
       </c>
       <c r="O29" t="n">
-        <v>0.4563427459604975</v>
+        <v>0.7142268503263578</v>
       </c>
     </row>
     <row r="30">
@@ -2060,10 +2060,10 @@
         <v>0.05</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
         <v>56</v>
@@ -2072,22 +2072,22 @@
         <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2209616741970988</v>
+        <v>0.3146572461488882</v>
       </c>
       <c r="K30" t="n">
-        <v>0.180161355283057</v>
+        <v>0.2400768937295654</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1768892117591615</v>
+        <v>0.2372465069759948</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7028547522549716</v>
+        <v>0.7820946327252301</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4744088713578391</v>
+        <v>0.435861227032099</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5917547909597367</v>
+        <v>0.7393694589501398</v>
       </c>
     </row>
     <row r="31">
@@ -2115,34 +2115,34 @@
         <v>0.05</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H31" t="n">
-        <v>45.83333333333334</v>
+        <v>49.64285714285715</v>
       </c>
       <c r="I31" t="n">
-        <v>13.40915939034045</v>
+        <v>17.70232891400428</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1617195320328492</v>
+        <v>0.9123478032866036</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1783532781764471</v>
+        <v>0.2338024224845934</v>
       </c>
       <c r="M31" t="n">
-        <v>0.696020969371498</v>
+        <v>0.7598856465951712</v>
       </c>
       <c r="N31" t="n">
-        <v>0.3570660613393661</v>
+        <v>0.4676291412024232</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7047448070789386</v>
+        <v>0.7552407317163961</v>
       </c>
     </row>
     <row r="32">
@@ -2170,34 +2170,34 @@
         <v>0.05</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="I32" t="n">
-        <v>9.41629792788369</v>
+        <v>10.66958293467931</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8210335882833985</v>
+        <v>0.8468886820124635</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3999705958906486</v>
+        <v>0.5391841538320152</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.8428334306489031</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5808794108782485</v>
+        <v>0.5600959964280652</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7268581750621723</v>
+        <v>0.819333745326341</v>
       </c>
     </row>
     <row r="33">
@@ -2225,34 +2225,34 @@
         <v>0.05</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>38.5</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>13.85339910154424</v>
       </c>
       <c r="J33" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="K33" t="n">
-        <v>2.099015430948417</v>
+        <v>1.798122934273217</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7799735108637011</v>
+        <v>0.6099187248303153</v>
       </c>
       <c r="M33" t="n">
-        <v>1.501425102377896</v>
+        <v>1.296566442979504</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6896153661181365</v>
+        <v>0.6832456367521271</v>
       </c>
       <c r="O33" t="n">
-        <v>1.431026035700699</v>
+        <v>1.290816454441452</v>
       </c>
     </row>
     <row r="34">
@@ -2280,34 +2280,34 @@
         <v>0.05</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>15</v>
+      </c>
+      <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="n">
-        <v/>
-      </c>
-      <c r="I34" t="n">
-        <v/>
-      </c>
       <c r="J34" t="n">
-        <v>1.021366535291565</v>
+        <v>0.8033992323085697</v>
       </c>
       <c r="K34" t="n">
-        <v>1.775651884656178</v>
+        <v>1.220289700704207</v>
       </c>
       <c r="L34" t="n">
         <v>0.4472211510464223</v>
       </c>
       <c r="M34" t="n">
-        <v>1.074975762493408</v>
+        <v>0.9484705495654446</v>
       </c>
       <c r="N34" t="n">
-        <v>0.5066180110351901</v>
+        <v>0.5020140765021653</v>
       </c>
       <c r="O34" t="n">
-        <v>1.0863828698298</v>
+        <v>0.9787543972515376</v>
       </c>
     </row>
     <row r="35">
@@ -2335,34 +2335,34 @@
         <v>0.05</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G35" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H35" t="n">
-        <v>22</v>
+        <v>24.38461538461538</v>
       </c>
       <c r="I35" t="n">
-        <v>3.295017884191656</v>
+        <v>6.475260155610757</v>
       </c>
       <c r="J35" t="n">
-        <v>0.533727686486196</v>
+        <v>0.4452065294449382</v>
       </c>
       <c r="K35" t="n">
-        <v>1.49205889472905</v>
+        <v>0.9877293814567232</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1766680669765602</v>
+        <v>0.2732336820009864</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8094513447340782</v>
+        <v>0.9439445633487472</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7169684154752586</v>
+        <v>0.630168272496189</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7757818647159882</v>
+        <v>0.9537365051754776</v>
       </c>
     </row>
     <row r="36">
@@ -2390,10 +2390,10 @@
         <v>0.05</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
         <v>60.66666666666666</v>
@@ -2402,22 +2402,22 @@
         <v>11.08552609887726</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2347463748366466</v>
+        <v>0.3072457440634565</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1804060172570415</v>
+        <v>0.2194112808755876</v>
       </c>
       <c r="L36" t="n">
-        <v>0.1752821467544498</v>
+        <v>0.2605881773731536</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7361035709314633</v>
+        <v>0.7950910799492387</v>
       </c>
       <c r="N36" t="n">
-        <v>0.51566757019427</v>
+        <v>0.4187450005295278</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6422764721385086</v>
+        <v>0.7750649706268949</v>
       </c>
     </row>
     <row r="37">
@@ -2445,34 +2445,34 @@
         <v>0.05</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>46</v>
+        <v>48.91666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>14.68332387438212</v>
+        <v>18.8257728187244</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1597860939976942</v>
+        <v>0.9117154154032876</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2005272103013687</v>
+        <v>0.247640707541535</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7532624842722424</v>
+        <v>0.763797982519849</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4417408676935017</v>
+        <v>0.5087149528737258</v>
       </c>
       <c r="O37" t="n">
-        <v>0.7223744251922304</v>
+        <v>0.8748540155400873</v>
       </c>
     </row>
     <row r="38">
@@ -2500,34 +2500,34 @@
         <v>0.05</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="I38" t="n">
-        <v>9.41629792788369</v>
+        <v>10.66958293467931</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8210335882833985</v>
+        <v>0.846870767044112</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3999705958906486</v>
+        <v>0.5391841538320152</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.845471059700435</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5808794108782485</v>
+        <v>0.5613417921707943</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7268581750621723</v>
+        <v>0.819333745326341</v>
       </c>
     </row>
     <row r="39">
@@ -2555,34 +2555,34 @@
         <v>0.05</v>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H39" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I39" t="n">
-        <v>32</v>
+        <v>23.11565126344775</v>
       </c>
       <c r="J39" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="K39" t="n">
-        <v>2.143521731111417</v>
+        <v>1.823052405821786</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5618029682163718</v>
+        <v>0.4436778167400766</v>
       </c>
       <c r="M39" t="n">
-        <v>1.444186909187633</v>
+        <v>1.257662594961341</v>
       </c>
       <c r="N39" t="n">
-        <v>0.7190814750073178</v>
+        <v>0.6942617144916274</v>
       </c>
       <c r="O39" t="n">
-        <v>1.391545000285481</v>
+        <v>1.183199506670446</v>
       </c>
     </row>
     <row r="40">
@@ -2610,34 +2610,34 @@
         <v>0.05</v>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v/>
+        <v>28.33333333333333</v>
       </c>
       <c r="I40" t="n">
-        <v/>
+        <v>11.32352516764202</v>
       </c>
       <c r="J40" t="n">
-        <v>1.949282572616417</v>
+        <v>1.609946685715318</v>
       </c>
       <c r="K40" t="n">
-        <v>1.975123865201877</v>
+        <v>1.744206500308552</v>
       </c>
       <c r="L40" t="n">
-        <v>1.0880424568776</v>
+        <v>0.9673318904358512</v>
       </c>
       <c r="M40" t="n">
-        <v>1.576745623147889</v>
+        <v>1.417631245983388</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6775744867245115</v>
+        <v>0.654938847370738</v>
       </c>
       <c r="O40" t="n">
-        <v>1.591149805826404</v>
+        <v>1.454772024699141</v>
       </c>
     </row>
     <row r="41">
@@ -2665,34 +2665,34 @@
         <v>0.05</v>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>35.25</v>
+        <v>39.18181818181818</v>
       </c>
       <c r="I41" t="n">
-        <v>14.90595518576384</v>
+        <v>15.26623238522424</v>
       </c>
       <c r="J41" t="n">
-        <v>1.563056352530661</v>
+        <v>1.412128529358507</v>
       </c>
       <c r="K41" t="n">
-        <v>2.094621870600836</v>
+        <v>1.778451478629357</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3703180525399001</v>
+        <v>0.4518026436608351</v>
       </c>
       <c r="M41" t="n">
-        <v>1.275320296244268</v>
+        <v>1.214469083767631</v>
       </c>
       <c r="N41" t="n">
-        <v>0.8492925438667411</v>
+        <v>0.7686952597029704</v>
       </c>
       <c r="O41" t="n">
-        <v>1.131169277713921</v>
+        <v>1.258926072907098</v>
       </c>
     </row>
     <row r="42">
@@ -2720,34 +2720,34 @@
         <v>0.05</v>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v/>
+        <v>23</v>
       </c>
       <c r="I42" t="n">
-        <v/>
+        <v>7.788880963698615</v>
       </c>
       <c r="J42" t="n">
-        <v>1.20123224871285</v>
+        <v>1.079054336554641</v>
       </c>
       <c r="K42" t="n">
-        <v>1.434847558669323</v>
+        <v>1.267752725358995</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5679865898263519</v>
+        <v>0.5792322545319998</v>
       </c>
       <c r="M42" t="n">
-        <v>1.37523996600375</v>
+        <v>1.221459067780741</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5026279187382272</v>
+        <v>0.5691337358279811</v>
       </c>
       <c r="O42" t="n">
-        <v>1.294030339259522</v>
+        <v>1.292341388886127</v>
       </c>
     </row>
     <row r="43">
@@ -2775,34 +2775,34 @@
         <v>0.05</v>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H43" t="n">
-        <v>45.83333333333334</v>
+        <v>49.64285714285715</v>
       </c>
       <c r="I43" t="n">
-        <v>13.40915939034045</v>
+        <v>17.70232891400428</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1617195320328492</v>
+        <v>0.9123478032866036</v>
       </c>
       <c r="L43" t="n">
-        <v>0.1783532781764471</v>
+        <v>0.2338024224845934</v>
       </c>
       <c r="M43" t="n">
-        <v>0.696020969371498</v>
+        <v>0.7598856465951712</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3570660613393661</v>
+        <v>0.4676291412024232</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7047448070789386</v>
+        <v>0.7552407317163961</v>
       </c>
     </row>
     <row r="44">
@@ -2830,34 +2830,34 @@
         <v>0.05</v>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="I44" t="n">
-        <v>9.41629792788369</v>
+        <v>10.66958293467931</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8210335882833985</v>
+        <v>0.8468886820124635</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3999705958906486</v>
+        <v>0.5391841538320152</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.8428334306489031</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5808794108782485</v>
+        <v>0.5600959964280652</v>
       </c>
       <c r="O44" t="n">
-        <v>0.7268581750621723</v>
+        <v>0.819333745326341</v>
       </c>
     </row>
     <row r="45">
@@ -2885,34 +2885,34 @@
         <v>0.05</v>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G45" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>38.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>13.85339910154424</v>
       </c>
       <c r="J45" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="K45" t="n">
-        <v>2.099015430948417</v>
+        <v>1.798122934273217</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7799735108637011</v>
+        <v>0.6099187248303153</v>
       </c>
       <c r="M45" t="n">
-        <v>1.501425102377896</v>
+        <v>1.296566442979504</v>
       </c>
       <c r="N45" t="n">
-        <v>0.6896153661181365</v>
+        <v>0.6832456367521271</v>
       </c>
       <c r="O45" t="n">
-        <v>1.431026035700699</v>
+        <v>1.290816454441452</v>
       </c>
     </row>
     <row r="46">
@@ -2940,34 +2940,34 @@
         <v>0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v/>
+        <v>35.33333333333334</v>
       </c>
       <c r="I46" t="n">
-        <v/>
+        <v>16.65999866613307</v>
       </c>
       <c r="J46" t="n">
-        <v>2.0573208415366</v>
+        <v>1.688443823970663</v>
       </c>
       <c r="K46" t="n">
-        <v>2.000717969285909</v>
+        <v>1.769642026734858</v>
       </c>
       <c r="L46" t="n">
-        <v>1.249596946142475</v>
+        <v>0.9987930748494316</v>
       </c>
       <c r="M46" t="n">
-        <v>1.600401412276286</v>
+        <v>1.43749085370591</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6791246806573854</v>
+        <v>0.6613696602432866</v>
       </c>
       <c r="O46" t="n">
-        <v>1.597965477689726</v>
+        <v>1.468319603925488</v>
       </c>
     </row>
     <row r="47">
@@ -2995,34 +2995,34 @@
         <v>0.05</v>
       </c>
       <c r="F47" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H47" t="n">
-        <v>33.25</v>
+        <v>41</v>
       </c>
       <c r="I47" t="n">
-        <v>12.13208555855093</v>
+        <v>18.62061418770264</v>
       </c>
       <c r="J47" t="n">
-        <v>1.608821480653673</v>
+        <v>1.411565748608577</v>
       </c>
       <c r="K47" t="n">
-        <v>2.099669976845704</v>
+        <v>1.7708201186996</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4582209833521145</v>
+        <v>0.5108689898569504</v>
       </c>
       <c r="M47" t="n">
-        <v>1.312146048873493</v>
+        <v>1.232008747455892</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8445486951425295</v>
+        <v>0.7602069748611581</v>
       </c>
       <c r="O47" t="n">
-        <v>1.223901132002764</v>
+        <v>1.275831244452053</v>
       </c>
     </row>
     <row r="48">
@@ -3050,34 +3050,34 @@
         <v>0.05</v>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v/>
+        <v>23</v>
       </c>
       <c r="I48" t="n">
-        <v/>
+        <v>7.788880963698615</v>
       </c>
       <c r="J48" t="n">
-        <v>1.266142192995252</v>
+        <v>1.177559786316756</v>
       </c>
       <c r="K48" t="n">
-        <v>1.440449383318984</v>
+        <v>1.264168312448876</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6187914807283521</v>
+        <v>0.6421792376232995</v>
       </c>
       <c r="M48" t="n">
-        <v>1.405119569320728</v>
+        <v>1.273762223299103</v>
       </c>
       <c r="N48" t="n">
-        <v>0.5066589779303134</v>
+        <v>0.5568920068362894</v>
       </c>
       <c r="O48" t="n">
-        <v>1.328876474933228</v>
+        <v>1.309412407863888</v>
       </c>
     </row>
     <row r="49">
@@ -3105,34 +3105,34 @@
         <v>0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>46</v>
+        <v>48.91666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>14.68332387438212</v>
+        <v>18.8257728187244</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1597860939976942</v>
+        <v>0.9117154154032876</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2005272103013687</v>
+        <v>0.247640707541535</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7532624842722424</v>
+        <v>0.763797982519849</v>
       </c>
       <c r="N49" t="n">
-        <v>0.4417408676935017</v>
+        <v>0.5087149528737258</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7223744251922304</v>
+        <v>0.8748540155400873</v>
       </c>
     </row>
     <row r="50">
@@ -3160,10 +3160,10 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -3172,22 +3172,22 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="K50" t="n">
-        <v>2.742852419065559</v>
+        <v>3.105429044317422</v>
       </c>
       <c r="L50" t="n">
-        <v>5.89993283523053</v>
+        <v>5.758550558615716</v>
       </c>
       <c r="M50" t="n">
-        <v>1.317351707463459</v>
+        <v>1.517158043021304</v>
       </c>
       <c r="N50" t="n">
-        <v>0.7139347720271464</v>
+        <v>0.6857660538955143</v>
       </c>
       <c r="O50" t="n">
-        <v>1.350054727209933</v>
+        <v>1.466435453829348</v>
       </c>
     </row>
     <row r="51">
@@ -3215,34 +3215,34 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H51" t="n">
-        <v>53.16666666666666</v>
+        <v>49.23076923076923</v>
       </c>
       <c r="I51" t="n">
-        <v>20.04508806554752</v>
+        <v>17.34781673762235</v>
       </c>
       <c r="J51" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="K51" t="n">
-        <v>2.045945379054419</v>
+        <v>2.159512591705487</v>
       </c>
       <c r="L51" t="n">
-        <v>1.630018682880554</v>
+        <v>1.994161778880693</v>
       </c>
       <c r="M51" t="n">
-        <v>1.342021237387835</v>
+        <v>1.332412035158513</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6949797653385544</v>
+        <v>0.756859960265062</v>
       </c>
       <c r="O51" t="n">
-        <v>1.202163501552793</v>
+        <v>1.394008983480658</v>
       </c>
     </row>
     <row r="52">
@@ -3270,34 +3270,34 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2.82842712474619</v>
       </c>
       <c r="J52" t="n">
-        <v>3.240208371863152</v>
+        <v>3.475260170951214</v>
       </c>
       <c r="K52" t="n">
-        <v>2.143197975192179</v>
+        <v>2.100585429960121</v>
       </c>
       <c r="L52" t="n">
-        <v>2.726195804510805</v>
+        <v>3.20914550340066</v>
       </c>
       <c r="M52" t="n">
-        <v>1.140927828707851</v>
+        <v>1.085844437904566</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4122830792086584</v>
+        <v>0.5778803178277001</v>
       </c>
       <c r="O52" t="n">
-        <v>1.063078713317094</v>
+        <v>1.040525709875192</v>
       </c>
     </row>
     <row r="53">
@@ -3325,34 +3325,34 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>9.41629792788369</v>
       </c>
       <c r="J53" t="n">
-        <v>3.432205526950077</v>
+        <v>3.774925420641969</v>
       </c>
       <c r="K53" t="n">
-        <v>3.144711859458278</v>
+        <v>2.954200460808634</v>
       </c>
       <c r="L53" t="n">
-        <v>2.059494943947829</v>
+        <v>2.349098127907904</v>
       </c>
       <c r="M53" t="n">
-        <v>1.515523008264331</v>
+        <v>1.59262414495807</v>
       </c>
       <c r="N53" t="n">
-        <v>0.7439301570998352</v>
+        <v>0.7582593281411404</v>
       </c>
       <c r="O53" t="n">
-        <v>1.384437770433524</v>
+        <v>1.415903087732233</v>
       </c>
     </row>
     <row r="54">
@@ -3380,34 +3380,34 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G54" t="n">
         <v>10</v>
       </c>
       <c r="H54" t="n">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>10.24499877989256</v>
       </c>
       <c r="J54" t="n">
-        <v>2.896880552434572</v>
+        <v>2.763048849043291</v>
       </c>
       <c r="K54" t="n">
-        <v>1.954531294542446</v>
+        <v>1.751747575586814</v>
       </c>
       <c r="L54" t="n">
-        <v>2.303893574014486</v>
+        <v>2.405487317291019</v>
       </c>
       <c r="M54" t="n">
-        <v>1.073487722064323</v>
+        <v>1.0118316150062</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6497581470274055</v>
+        <v>0.6445039626393196</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9969791188368664</v>
+        <v>1.002461077617321</v>
       </c>
     </row>
     <row r="55">
@@ -3435,34 +3435,34 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>16.77961726487096</v>
       </c>
       <c r="J55" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="K55" t="n">
-        <v>1.586092682059829</v>
+        <v>1.592393308572874</v>
       </c>
       <c r="L55" t="n">
-        <v>2.485069376759622</v>
+        <v>2.664926909198268</v>
       </c>
       <c r="M55" t="n">
-        <v>1.180834807809197</v>
+        <v>1.132387135255874</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6357605245011929</v>
+        <v>0.6162615897572524</v>
       </c>
       <c r="O55" t="n">
-        <v>1.187060551392918</v>
+        <v>1.098992758402416</v>
       </c>
     </row>
     <row r="56">
@@ -3490,10 +3490,10 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>13</v>
@@ -3502,22 +3502,22 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="K56" t="n">
-        <v>2.733374706387525</v>
+        <v>3.105975329526104</v>
       </c>
       <c r="L56" t="n">
-        <v>5.89993283523053</v>
+        <v>5.758550558615716</v>
       </c>
       <c r="M56" t="n">
-        <v>1.406285393529407</v>
+        <v>1.565050836717096</v>
       </c>
       <c r="N56" t="n">
-        <v>0.6685236575556621</v>
+        <v>0.694404276202518</v>
       </c>
       <c r="O56" t="n">
-        <v>1.444384951819221</v>
+        <v>1.466435453829348</v>
       </c>
     </row>
     <row r="57">
@@ -3545,34 +3545,34 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H57" t="n">
-        <v>41.75</v>
+        <v>47.08333333333334</v>
       </c>
       <c r="I57" t="n">
-        <v>13.62672007491164</v>
+        <v>19.39698573375656</v>
       </c>
       <c r="J57" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="K57" t="n">
-        <v>2.084004628984987</v>
+        <v>2.507106411214153</v>
       </c>
       <c r="L57" t="n">
-        <v>1.632824216897371</v>
+        <v>1.931807420308417</v>
       </c>
       <c r="M57" t="n">
-        <v>1.284471615179526</v>
+        <v>1.343571408135632</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7400228063617381</v>
+        <v>0.8752175471517124</v>
       </c>
       <c r="O57" t="n">
-        <v>1.023223877744781</v>
+        <v>1.20926371518454</v>
       </c>
     </row>
     <row r="58">
@@ -3600,34 +3600,34 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H58" t="n">
-        <v>71</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>6.309164410249233</v>
       </c>
       <c r="J58" t="n">
-        <v>3.271126748173042</v>
+        <v>3.295829362112158</v>
       </c>
       <c r="K58" t="n">
-        <v>2.263258787748118</v>
+        <v>2.354443485581544</v>
       </c>
       <c r="L58" t="n">
-        <v>2.610675148609182</v>
+        <v>2.819745422176961</v>
       </c>
       <c r="M58" t="n">
-        <v>1.06113533475451</v>
+        <v>1.042008266069966</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4309429046600291</v>
+        <v>0.5631790891802148</v>
       </c>
       <c r="O58" t="n">
-        <v>1.055491355244758</v>
+        <v>1.037635864146845</v>
       </c>
     </row>
     <row r="59">
@@ -3655,34 +3655,34 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H59" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>9.137833441248532</v>
       </c>
       <c r="J59" t="n">
-        <v>3.439709319043941</v>
+        <v>3.998993936933476</v>
       </c>
       <c r="K59" t="n">
-        <v>2.763531872881493</v>
+        <v>3.419394016625946</v>
       </c>
       <c r="L59" t="n">
-        <v>2.249627841072291</v>
+        <v>2.376107245244296</v>
       </c>
       <c r="M59" t="n">
-        <v>1.448707858961522</v>
+        <v>1.510129805005717</v>
       </c>
       <c r="N59" t="n">
-        <v>0.7931351774243497</v>
+        <v>0.7700481554517153</v>
       </c>
       <c r="O59" t="n">
-        <v>1.218846150055394</v>
+        <v>1.383252207756304</v>
       </c>
     </row>
     <row r="60">
@@ -3710,34 +3710,34 @@
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H60" t="n">
-        <v>53.66666666666666</v>
+        <v>56.5</v>
       </c>
       <c r="I60" t="n">
-        <v>11.02522360569415</v>
+        <v>10.73545527679194</v>
       </c>
       <c r="J60" t="n">
-        <v>3.08532419385823</v>
+        <v>3.29777010421497</v>
       </c>
       <c r="K60" t="n">
-        <v>1.789691436124854</v>
+        <v>1.835207445040508</v>
       </c>
       <c r="L60" t="n">
-        <v>2.928111025798039</v>
+        <v>3.086073375669116</v>
       </c>
       <c r="M60" t="n">
-        <v>1.084792191040415</v>
+        <v>1.223461421858214</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6439741188527565</v>
+        <v>0.6259589158200932</v>
       </c>
       <c r="O60" t="n">
-        <v>1.050822469154777</v>
+        <v>1.347753458204605</v>
       </c>
     </row>
     <row r="61">
@@ -3765,34 +3765,34 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H61" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="I61" t="n">
-        <v>16.30950643030009</v>
+        <v>14.15097169808491</v>
       </c>
       <c r="J61" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="K61" t="n">
-        <v>1.550239280158219</v>
+        <v>1.600830082040024</v>
       </c>
       <c r="L61" t="n">
-        <v>2.225512733803724</v>
+        <v>2.694279803426539</v>
       </c>
       <c r="M61" t="n">
-        <v>1.083896779809906</v>
+        <v>1.089443516269316</v>
       </c>
       <c r="N61" t="n">
-        <v>0.5573307361976979</v>
+        <v>0.580774163763965</v>
       </c>
       <c r="O61" t="n">
-        <v>1.030640565988385</v>
+        <v>1.047832667149038</v>
       </c>
     </row>
     <row r="62">
@@ -3820,10 +3820,10 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
         <v>13</v>
@@ -3832,22 +3832,22 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="K62" t="n">
-        <v>2.742852419065559</v>
+        <v>3.105429044317422</v>
       </c>
       <c r="L62" t="n">
-        <v>5.89993283523053</v>
+        <v>5.758550558615716</v>
       </c>
       <c r="M62" t="n">
-        <v>1.317351707463459</v>
+        <v>1.517158043021304</v>
       </c>
       <c r="N62" t="n">
-        <v>0.7139347720271464</v>
+        <v>0.6857660538955143</v>
       </c>
       <c r="O62" t="n">
-        <v>1.350054727209933</v>
+        <v>1.466435453829348</v>
       </c>
     </row>
     <row r="63">
@@ -3875,34 +3875,34 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H63" t="n">
-        <v>53.16666666666666</v>
+        <v>49.23076923076923</v>
       </c>
       <c r="I63" t="n">
-        <v>20.04508806554752</v>
+        <v>17.34781673762235</v>
       </c>
       <c r="J63" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="K63" t="n">
-        <v>2.045945379054419</v>
+        <v>2.159512591705487</v>
       </c>
       <c r="L63" t="n">
-        <v>1.630018682880554</v>
+        <v>1.994161778880693</v>
       </c>
       <c r="M63" t="n">
-        <v>1.342021237387835</v>
+        <v>1.332412035158513</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6949797653385544</v>
+        <v>0.756859960265062</v>
       </c>
       <c r="O63" t="n">
-        <v>1.202163501552793</v>
+        <v>1.394008983480658</v>
       </c>
     </row>
     <row r="64">
@@ -3930,34 +3930,34 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H64" t="n">
-        <v>43.14285714285715</v>
+        <v>40.71428571428572</v>
       </c>
       <c r="I64" t="n">
-        <v>11.51928285749683</v>
+        <v>15.22417518961476</v>
       </c>
       <c r="J64" t="n">
-        <v>2.87457346701875</v>
+        <v>2.74180848964904</v>
       </c>
       <c r="K64" t="n">
-        <v>3.651472055949827</v>
+        <v>3.069245864978113</v>
       </c>
       <c r="L64" t="n">
-        <v>1.03872770634994</v>
+        <v>1.534021407964087</v>
       </c>
       <c r="M64" t="n">
-        <v>1.263810768803331</v>
+        <v>1.295593505125749</v>
       </c>
       <c r="N64" t="n">
-        <v>1.107538032114149</v>
+        <v>0.9660996283484788</v>
       </c>
       <c r="O64" t="n">
-        <v>0.992164581789396</v>
+        <v>1.18353852497637</v>
       </c>
     </row>
     <row r="65">
@@ -3985,34 +3985,34 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H65" t="n">
-        <v>41</v>
+        <v>44.4</v>
       </c>
       <c r="I65" t="n">
-        <v>4.08248290463863</v>
+        <v>7.49933330370107</v>
       </c>
       <c r="J65" t="n">
-        <v>1.913234301077092</v>
+        <v>2.184474140912512</v>
       </c>
       <c r="K65" t="n">
-        <v>1.819979554387466</v>
+        <v>1.946977199743929</v>
       </c>
       <c r="L65" t="n">
-        <v>1.178256962375906</v>
+        <v>1.929767772300698</v>
       </c>
       <c r="M65" t="n">
-        <v>1.159418188992784</v>
+        <v>1.240927668374411</v>
       </c>
       <c r="N65" t="n">
-        <v>0.6712682423714381</v>
+        <v>0.6707819085259574</v>
       </c>
       <c r="O65" t="n">
-        <v>1.01215240691007</v>
+        <v>1.018735720572174</v>
       </c>
     </row>
     <row r="66">
@@ -4040,34 +4040,34 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H66" t="n">
-        <v/>
+        <v>44</v>
       </c>
       <c r="I66" t="n">
-        <v/>
+        <v>22.50185177565023</v>
       </c>
       <c r="J66" t="n">
-        <v>3.552351406613214</v>
+        <v>3.289909449212436</v>
       </c>
       <c r="K66" t="n">
-        <v>2.647058449593157</v>
+        <v>2.953168847259541</v>
       </c>
       <c r="L66" t="n">
-        <v>2.360368098963191</v>
+        <v>2.009963487462677</v>
       </c>
       <c r="M66" t="n">
-        <v>1.576992306451476</v>
+        <v>1.49482836036725</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6752925000603893</v>
+        <v>0.7687537474492777</v>
       </c>
       <c r="O66" t="n">
-        <v>1.411049096099251</v>
+        <v>1.407362193631173</v>
       </c>
     </row>
     <row r="67">
@@ -4095,34 +4095,34 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>45</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>16.77961726487096</v>
       </c>
       <c r="J67" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="K67" t="n">
-        <v>1.586092682059829</v>
+        <v>1.592393308572874</v>
       </c>
       <c r="L67" t="n">
-        <v>2.485069376759622</v>
+        <v>2.664926909198268</v>
       </c>
       <c r="M67" t="n">
-        <v>1.180834807809197</v>
+        <v>1.132387135255874</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6357605245011929</v>
+        <v>0.6162615897572524</v>
       </c>
       <c r="O67" t="n">
-        <v>1.187060551392918</v>
+        <v>1.098992758402416</v>
       </c>
     </row>
     <row r="68">
@@ -4150,10 +4150,10 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>13</v>
@@ -4162,22 +4162,22 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="K68" t="n">
-        <v>2.733374706387525</v>
+        <v>3.105975329526104</v>
       </c>
       <c r="L68" t="n">
-        <v>5.89993283523053</v>
+        <v>5.758550558615716</v>
       </c>
       <c r="M68" t="n">
-        <v>1.406285393529407</v>
+        <v>1.565050836717096</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6685236575556621</v>
+        <v>0.694404276202518</v>
       </c>
       <c r="O68" t="n">
-        <v>1.444384951819221</v>
+        <v>1.466435453829348</v>
       </c>
     </row>
     <row r="69">
@@ -4205,34 +4205,34 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H69" t="n">
-        <v>41.75</v>
+        <v>47.08333333333334</v>
       </c>
       <c r="I69" t="n">
-        <v>13.62672007491164</v>
+        <v>19.39698573375656</v>
       </c>
       <c r="J69" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="K69" t="n">
-        <v>2.084004628984987</v>
+        <v>2.507106411214153</v>
       </c>
       <c r="L69" t="n">
-        <v>1.632824216897371</v>
+        <v>1.931807420308417</v>
       </c>
       <c r="M69" t="n">
-        <v>1.284471615179526</v>
+        <v>1.343571408135632</v>
       </c>
       <c r="N69" t="n">
-        <v>0.7400228063617381</v>
+        <v>0.8752175471517124</v>
       </c>
       <c r="O69" t="n">
-        <v>1.023223877744781</v>
+        <v>1.20926371518454</v>
       </c>
     </row>
     <row r="70">
@@ -4260,34 +4260,34 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H70" t="n">
-        <v>43.16666666666666</v>
+        <v>39.5</v>
       </c>
       <c r="I70" t="n">
-        <v>13.19616947787838</v>
+        <v>11.02648327134873</v>
       </c>
       <c r="J70" t="n">
-        <v>2.621339418098632</v>
+        <v>3.017672585517013</v>
       </c>
       <c r="K70" t="n">
-        <v>2.71022749589565</v>
+        <v>2.787365949338098</v>
       </c>
       <c r="L70" t="n">
-        <v>1.661319394702623</v>
+        <v>2.106175884482086</v>
       </c>
       <c r="M70" t="n">
-        <v>1.218002177386809</v>
+        <v>1.373860453321078</v>
       </c>
       <c r="N70" t="n">
-        <v>0.9546854301216388</v>
+        <v>0.9268220871923872</v>
       </c>
       <c r="O70" t="n">
-        <v>1.201742664400272</v>
+        <v>1.407810482470649</v>
       </c>
     </row>
     <row r="71">
@@ -4315,34 +4315,34 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G71" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H71" t="n">
-        <v>48</v>
+        <v>39.71428571428572</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>7.832428663927313</v>
       </c>
       <c r="J71" t="n">
-        <v>2.491488891931755</v>
+        <v>2.217037544021018</v>
       </c>
       <c r="K71" t="n">
-        <v>2.08021794678444</v>
+        <v>2.026311386462385</v>
       </c>
       <c r="L71" t="n">
-        <v>1.577057192398428</v>
+        <v>1.270495952001356</v>
       </c>
       <c r="M71" t="n">
-        <v>1.243380091473654</v>
+        <v>1.206463788967818</v>
       </c>
       <c r="N71" t="n">
-        <v>0.7312737564177788</v>
+        <v>0.6891996808934479</v>
       </c>
       <c r="O71" t="n">
-        <v>1.024619891958449</v>
+        <v>1.015590174986034</v>
       </c>
     </row>
     <row r="72">
@@ -4370,34 +4370,34 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G72" t="n">
+        <v>4</v>
+      </c>
+      <c r="H72" t="n">
+        <v>51</v>
+      </c>
+      <c r="I72" t="n">
         <v>5</v>
       </c>
-      <c r="H72" t="n">
-        <v>46</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
       <c r="J72" t="n">
-        <v>4.133461220047512</v>
+        <v>3.489242329377287</v>
       </c>
       <c r="K72" t="n">
-        <v>3.171880657996429</v>
+        <v>2.704209815002421</v>
       </c>
       <c r="L72" t="n">
-        <v>4.507927742736543</v>
+        <v>2.300463089477216</v>
       </c>
       <c r="M72" t="n">
-        <v>1.712979624080441</v>
+        <v>1.616782849248249</v>
       </c>
       <c r="N72" t="n">
-        <v>0.8527921602054428</v>
+        <v>0.6854058878344278</v>
       </c>
       <c r="O72" t="n">
-        <v>1.681100734509752</v>
+        <v>1.410753451888257</v>
       </c>
     </row>
     <row r="73">
@@ -4425,34 +4425,34 @@
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G73" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H73" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="I73" t="n">
-        <v>16.30950643030009</v>
+        <v>14.15097169808491</v>
       </c>
       <c r="J73" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="K73" t="n">
-        <v>1.550239280158219</v>
+        <v>1.600830082040024</v>
       </c>
       <c r="L73" t="n">
-        <v>2.225512733803724</v>
+        <v>2.694279803426539</v>
       </c>
       <c r="M73" t="n">
-        <v>1.083896779809906</v>
+        <v>1.089443516269316</v>
       </c>
       <c r="N73" t="n">
-        <v>0.5573307361976979</v>
+        <v>0.580774163763965</v>
       </c>
       <c r="O73" t="n">
-        <v>1.030640565988385</v>
+        <v>1.047832667149038</v>
       </c>
     </row>
     <row r="74">
@@ -4480,10 +4480,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
         <v>13</v>
@@ -4492,22 +4492,22 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="K74" t="n">
-        <v>1.109101538046367</v>
+        <v>1.04761786828315</v>
       </c>
       <c r="L74" t="n">
-        <v>3.071705632925936</v>
+        <v>3.099847073963597</v>
       </c>
       <c r="M74" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7459414848044662</v>
       </c>
       <c r="N74" t="n">
-        <v>0.4120599349096632</v>
+        <v>0.4370916791499054</v>
       </c>
       <c r="O74" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.7382881684926865</v>
       </c>
     </row>
     <row r="75">
@@ -4535,34 +4535,34 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G75" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H75" t="n">
-        <v>42.23076923076923</v>
+        <v>41.12121212121212</v>
       </c>
       <c r="I75" t="n">
-        <v>19.14380336037204</v>
+        <v>16.27185258074661</v>
       </c>
       <c r="J75" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="K75" t="n">
-        <v>1.314460633182515</v>
+        <v>1.195437175796858</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3112169020886974</v>
+        <v>0.1614449782037064</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3322798282634774</v>
+        <v>0.2804080072741859</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4530046976070429</v>
+        <v>0.4242438643561418</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0679846520971729</v>
+        <v>0.0412575974598179</v>
       </c>
     </row>
     <row r="76">
@@ -4590,34 +4590,34 @@
         <v>0.5</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G76" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H76" t="n">
-        <v>48.5625</v>
+        <v>41.91891891891892</v>
       </c>
       <c r="I76" t="n">
-        <v>17.20090386433225</v>
+        <v>14.8858328773665</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5244680645286115</v>
+        <v>0.7841264251850864</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9794122159806824</v>
+        <v>1.316460569888938</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0652309049777479</v>
+        <v>0.0647775721881118</v>
       </c>
       <c r="M76" t="n">
-        <v>0.156854979541749</v>
+        <v>0.2689669727369452</v>
       </c>
       <c r="N76" t="n">
-        <v>0.3475351967629476</v>
+        <v>0.4995543136761763</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0194788563541278</v>
+        <v>0.0193645840179197</v>
       </c>
     </row>
     <row r="77">
@@ -4645,34 +4645,34 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G77" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H77" t="n">
-        <v>28.75</v>
+        <v>31.95238095238096</v>
       </c>
       <c r="I77" t="n">
-        <v>5.539629951540085</v>
+        <v>12.33066711390438</v>
       </c>
       <c r="J77" t="n">
-        <v>0.4342414697038436</v>
+        <v>0.4127514240458644</v>
       </c>
       <c r="K77" t="n">
-        <v>0.8017289546821587</v>
+        <v>0.8392475863128368</v>
       </c>
       <c r="L77" t="n">
-        <v>0.07688512984029081</v>
+        <v>0.0708473466641881</v>
       </c>
       <c r="M77" t="n">
-        <v>0.1291979132700974</v>
+        <v>0.1330196891303455</v>
       </c>
       <c r="N77" t="n">
-        <v>0.2797808915450754</v>
+        <v>0.3103446527695052</v>
       </c>
       <c r="O77" t="n">
-        <v>0.0224532720852124</v>
+        <v>0.0209267702352455</v>
       </c>
     </row>
     <row r="78">
@@ -4700,34 +4700,34 @@
         <v>0.5</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G78" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H78" t="n">
-        <v>34.38888888888889</v>
+        <v>37.06521739130435</v>
       </c>
       <c r="I78" t="n">
-        <v>9.013193347587061</v>
+        <v>10.45570818492909</v>
       </c>
       <c r="J78" t="n">
-        <v>0.2108504709006535</v>
+        <v>0.229229150615906</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5604297647753986</v>
+        <v>0.6044667537859484</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0508448961710592</v>
+        <v>0.048830439060993</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0683618646086024</v>
+        <v>0.07622401556846729</v>
       </c>
       <c r="N78" t="n">
-        <v>0.2056667391338733</v>
+        <v>0.2228594908639893</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0156678169269036</v>
+        <v>0.015116320538944</v>
       </c>
     </row>
     <row r="79">
@@ -4755,34 +4755,34 @@
         <v>0.5</v>
       </c>
       <c r="F79" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G79" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H79" t="n">
-        <v>50.66666666666666</v>
+        <v>53.66666666666666</v>
       </c>
       <c r="I79" t="n">
-        <v>13.91242450313947</v>
+        <v>15.13458144632866</v>
       </c>
       <c r="J79" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="K79" t="n">
-        <v>0.538294287653132</v>
+        <v>0.5844586752804273</v>
       </c>
       <c r="L79" t="n">
-        <v>1.01415342185068</v>
+        <v>0.9682526818851368</v>
       </c>
       <c r="M79" t="n">
-        <v>0.1685217717513979</v>
+        <v>0.1623611943016591</v>
       </c>
       <c r="N79" t="n">
-        <v>0.0635064252787535</v>
+        <v>0.1212946864832229</v>
       </c>
       <c r="O79" t="n">
-        <v>0.1579523625952787</v>
+        <v>0.1549824616465873</v>
       </c>
     </row>
     <row r="80">
@@ -4810,10 +4810,10 @@
         <v>0.5</v>
       </c>
       <c r="F80" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
         <v>13</v>
@@ -4822,22 +4822,22 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="K80" t="n">
-        <v>1.109101538046367</v>
+        <v>1.048625545293653</v>
       </c>
       <c r="L80" t="n">
-        <v>3.071705632925936</v>
+        <v>3.099847073963597</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7554543100898569</v>
       </c>
       <c r="N80" t="n">
-        <v>0.4120599349096632</v>
+        <v>0.443926960048315</v>
       </c>
       <c r="O80" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.7382881684926865</v>
       </c>
     </row>
     <row r="81">
@@ -4865,34 +4865,34 @@
         <v>0.5</v>
       </c>
       <c r="F81" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G81" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H81" t="n">
-        <v>39.35714285714285</v>
+        <v>36.64705882352941</v>
       </c>
       <c r="I81" t="n">
-        <v>13.69362282679237</v>
+        <v>11.88147929228555</v>
       </c>
       <c r="J81" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="K81" t="n">
-        <v>1.382314388100351</v>
+        <v>1.248624579917453</v>
       </c>
       <c r="L81" t="n">
-        <v>0.1912572231738001</v>
+        <v>0.1407555553112911</v>
       </c>
       <c r="M81" t="n">
-        <v>0.327565001173614</v>
+        <v>0.2956148435667205</v>
       </c>
       <c r="N81" t="n">
-        <v>0.5394379015089441</v>
+        <v>0.4700450173761638</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0459906284027332</v>
+        <v>0.0369987805621225</v>
       </c>
     </row>
     <row r="82">
@@ -4920,34 +4920,34 @@
         <v>0.5</v>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H82" t="n">
-        <v>42.15384615384615</v>
+        <v>40.6764705882353</v>
       </c>
       <c r="I82" t="n">
-        <v>12.03741701047296</v>
+        <v>11.87364998700235</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8731825644241763</v>
+        <v>0.8257406734139249</v>
       </c>
       <c r="K82" t="n">
-        <v>1.171436895706236</v>
+        <v>1.267284771389109</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1379900037868702</v>
+        <v>0.1248836489877178</v>
       </c>
       <c r="M82" t="n">
-        <v>0.2381197770737083</v>
+        <v>0.2605197291370963</v>
       </c>
       <c r="N82" t="n">
-        <v>0.3941863802748001</v>
+        <v>0.4720817649150847</v>
       </c>
       <c r="O82" t="n">
-        <v>0.0364214409945682</v>
+        <v>0.033567744584522</v>
       </c>
     </row>
     <row r="83">
@@ -4975,34 +4975,34 @@
         <v>0.5</v>
       </c>
       <c r="F83" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G83" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H83" t="n">
-        <v>30.88235294117647</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="I83" t="n">
-        <v>9.16439627960021</v>
+        <v>10.17680992833512</v>
       </c>
       <c r="J83" t="n">
-        <v>0.268652913319751</v>
+        <v>0.3117104398512642</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5564908469052946</v>
+        <v>0.6215500683411059</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0914621300609703</v>
+        <v>0.0861062885459138</v>
       </c>
       <c r="M83" t="n">
-        <v>0.0784704539736349</v>
+        <v>0.09047272338471481</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1969996789057422</v>
+        <v>0.2182767943353318</v>
       </c>
       <c r="O83" t="n">
-        <v>0.0259848208758169</v>
+        <v>0.0247155189362528</v>
       </c>
     </row>
     <row r="84">
@@ -5030,34 +5030,34 @@
         <v>0.5</v>
       </c>
       <c r="F84" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H84" t="n">
-        <v>35.52941176470588</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="I84" t="n">
-        <v>9.088568430977867</v>
+        <v>10.56005394063046</v>
       </c>
       <c r="J84" t="n">
-        <v>0.5710505853853267</v>
+        <v>0.5480811890201259</v>
       </c>
       <c r="K84" t="n">
-        <v>1.565590038268745</v>
+        <v>1.232381430593392</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0644408651837378</v>
+        <v>0.1053199456236506</v>
       </c>
       <c r="M84" t="n">
-        <v>0.2169922033723937</v>
+        <v>0.1859561005550112</v>
       </c>
       <c r="N84" t="n">
-        <v>0.6540183741497566</v>
+        <v>0.4824334211753918</v>
       </c>
       <c r="O84" t="n">
-        <v>0.0192827247913668</v>
+        <v>0.029223004153171</v>
       </c>
     </row>
     <row r="85">
@@ -5085,34 +5085,34 @@
         <v>0.5</v>
       </c>
       <c r="F85" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G85" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H85" t="n">
-        <v>53.75</v>
+        <v>50.84615384615385</v>
       </c>
       <c r="I85" t="n">
-        <v>14.8891739193281</v>
+        <v>16.28990321473894</v>
       </c>
       <c r="J85" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5573254569271926</v>
+        <v>0.5653385818479379</v>
       </c>
       <c r="L85" t="n">
-        <v>0.8891379295116182</v>
+        <v>0.8654224368507433</v>
       </c>
       <c r="M85" t="n">
-        <v>0.1623807660752869</v>
+        <v>0.1504649048763514</v>
       </c>
       <c r="N85" t="n">
-        <v>0.06900520215139951</v>
+        <v>0.07040775724912619</v>
       </c>
       <c r="O85" t="n">
-        <v>0.1448903727100377</v>
+        <v>0.1417572110024848</v>
       </c>
     </row>
     <row r="86">
@@ -5140,10 +5140,10 @@
         <v>0.5</v>
       </c>
       <c r="F86" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>13</v>
@@ -5152,22 +5152,22 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="K86" t="n">
-        <v>1.109101538046367</v>
+        <v>1.04761786828315</v>
       </c>
       <c r="L86" t="n">
-        <v>3.071705632925936</v>
+        <v>3.099847073963597</v>
       </c>
       <c r="M86" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7459414848044662</v>
       </c>
       <c r="N86" t="n">
-        <v>0.4120599349096632</v>
+        <v>0.4370916791499054</v>
       </c>
       <c r="O86" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.7382881684926865</v>
       </c>
     </row>
     <row r="87">
@@ -5195,34 +5195,34 @@
         <v>0.5</v>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G87" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H87" t="n">
-        <v>42.23076923076923</v>
+        <v>41.12121212121212</v>
       </c>
       <c r="I87" t="n">
-        <v>19.14380336037204</v>
+        <v>16.27185258074661</v>
       </c>
       <c r="J87" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="K87" t="n">
-        <v>1.314460633182515</v>
+        <v>1.195437175796858</v>
       </c>
       <c r="L87" t="n">
-        <v>0.3112169020886974</v>
+        <v>0.1614449782037064</v>
       </c>
       <c r="M87" t="n">
-        <v>0.3322798282634774</v>
+        <v>0.2804080072741859</v>
       </c>
       <c r="N87" t="n">
-        <v>0.4530046976070429</v>
+        <v>0.4242438643561418</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0679846520971729</v>
+        <v>0.0412575974598179</v>
       </c>
     </row>
     <row r="88">
@@ -5250,34 +5250,34 @@
         <v>0.5</v>
       </c>
       <c r="F88" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G88" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H88" t="n">
-        <v>36.25</v>
+        <v>34.88461538461539</v>
       </c>
       <c r="I88" t="n">
-        <v>16.59882023920174</v>
+        <v>14.46833923560982</v>
       </c>
       <c r="J88" t="n">
-        <v>1.111669912723853</v>
+        <v>1.342777348916411</v>
       </c>
       <c r="K88" t="n">
-        <v>1.486215055707723</v>
+        <v>1.58669226771708</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1950380693273641</v>
+        <v>0.2995515689682162</v>
       </c>
       <c r="M88" t="n">
-        <v>0.3601819609140434</v>
+        <v>0.4730463666638156</v>
       </c>
       <c r="N88" t="n">
-        <v>0.5500271513148058</v>
+        <v>0.6177840453136363</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0474187114516113</v>
+        <v>0.06600376961399811</v>
       </c>
     </row>
     <row r="89">
@@ -5305,34 +5305,34 @@
         <v>0.5</v>
       </c>
       <c r="F89" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G89" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H89" t="n">
-        <v>35.25</v>
+        <v>34.2258064516129</v>
       </c>
       <c r="I89" t="n">
-        <v>13.70599017461587</v>
+        <v>11.8667594223674</v>
       </c>
       <c r="J89" t="n">
-        <v>1.082900978758997</v>
+        <v>1.010267106779598</v>
       </c>
       <c r="K89" t="n">
-        <v>1.293958567212334</v>
+        <v>1.269043974741976</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1017284380083904</v>
+        <v>0.136583916204128</v>
       </c>
       <c r="M89" t="n">
-        <v>0.3625516561642117</v>
+        <v>0.3141753362436059</v>
       </c>
       <c r="N89" t="n">
-        <v>0.4532512753319288</v>
+        <v>0.4415301944373104</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0281666477612789</v>
+        <v>0.0361157457844701</v>
       </c>
     </row>
     <row r="90">
@@ -5360,34 +5360,34 @@
         <v>0.5</v>
       </c>
       <c r="F90" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G90" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H90" t="n">
-        <v>33.66666666666666</v>
+        <v>37.75757575757576</v>
       </c>
       <c r="I90" t="n">
-        <v>12.4186240067981</v>
+        <v>15.80569575708304</v>
       </c>
       <c r="J90" t="n">
-        <v>1.052165108906756</v>
+        <v>0.901472723746057</v>
       </c>
       <c r="K90" t="n">
-        <v>1.526952099257635</v>
+        <v>1.304599409390515</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0421539671334412</v>
+        <v>0.1015716692349824</v>
       </c>
       <c r="M90" t="n">
-        <v>0.3389114149749481</v>
+        <v>0.2781181955099485</v>
       </c>
       <c r="N90" t="n">
-        <v>0.5599801888128962</v>
+        <v>0.4584368586098143</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0132480210721311</v>
+        <v>0.0282881472472146</v>
       </c>
     </row>
     <row r="91">
@@ -5415,34 +5415,34 @@
         <v>0.5</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G91" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H91" t="n">
-        <v>50.66666666666666</v>
+        <v>53.66666666666666</v>
       </c>
       <c r="I91" t="n">
-        <v>13.91242450313947</v>
+        <v>15.13458144632866</v>
       </c>
       <c r="J91" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="K91" t="n">
-        <v>0.538294287653132</v>
+        <v>0.5844586752804273</v>
       </c>
       <c r="L91" t="n">
-        <v>1.01415342185068</v>
+        <v>0.9682526818851368</v>
       </c>
       <c r="M91" t="n">
-        <v>0.1685217717513979</v>
+        <v>0.1623611943016591</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0635064252787535</v>
+        <v>0.1212946864832229</v>
       </c>
       <c r="O91" t="n">
-        <v>0.1579523625952787</v>
+        <v>0.1549824616465873</v>
       </c>
     </row>
     <row r="92">
@@ -5470,10 +5470,10 @@
         <v>0.5</v>
       </c>
       <c r="F92" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>13</v>
@@ -5482,22 +5482,22 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="K92" t="n">
-        <v>1.109101538046367</v>
+        <v>1.048625545293653</v>
       </c>
       <c r="L92" t="n">
-        <v>3.071705632925936</v>
+        <v>3.099847073963597</v>
       </c>
       <c r="M92" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7554543100898569</v>
       </c>
       <c r="N92" t="n">
-        <v>0.4120599349096632</v>
+        <v>0.443926960048315</v>
       </c>
       <c r="O92" t="n">
-        <v>0.4895158072032382</v>
+        <v>0.7382881684926865</v>
       </c>
     </row>
     <row r="93">
@@ -5525,34 +5525,34 @@
         <v>0.5</v>
       </c>
       <c r="F93" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G93" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H93" t="n">
-        <v>39.35714285714285</v>
+        <v>36.64705882352941</v>
       </c>
       <c r="I93" t="n">
-        <v>13.69362282679237</v>
+        <v>11.88147929228555</v>
       </c>
       <c r="J93" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="K93" t="n">
-        <v>1.382314388100351</v>
+        <v>1.248624579917453</v>
       </c>
       <c r="L93" t="n">
-        <v>0.1912572231738001</v>
+        <v>0.1407555553112911</v>
       </c>
       <c r="M93" t="n">
-        <v>0.327565001173614</v>
+        <v>0.2956148435667205</v>
       </c>
       <c r="N93" t="n">
-        <v>0.5394379015089441</v>
+        <v>0.4700450173761638</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0459906284027332</v>
+        <v>0.0369987805621225</v>
       </c>
     </row>
     <row r="94">
@@ -5580,31 +5580,31 @@
         <v>0.5</v>
       </c>
       <c r="F94" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G94" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H94" t="n">
-        <v>38.4</v>
+        <v>39.55882352941177</v>
       </c>
       <c r="I94" t="n">
-        <v>15.08995250710441</v>
+        <v>15.82661789233678</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9382823360174214</v>
+        <v>0.9858360467114322</v>
       </c>
       <c r="K94" t="n">
-        <v>1.634961158999424</v>
+        <v>1.520033579472108</v>
       </c>
       <c r="L94" t="n">
         <v>0.160831005761207</v>
       </c>
       <c r="M94" t="n">
-        <v>0.342977740623145</v>
+        <v>0.3511914870750401</v>
       </c>
       <c r="N94" t="n">
-        <v>0.6417732945183237</v>
+        <v>0.5967852584008836</v>
       </c>
       <c r="O94" t="n">
         <v>0.0411239186559642</v>
@@ -5635,34 +5635,34 @@
         <v>0.5</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G95" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H95" t="n">
-        <v>33.75</v>
+        <v>33.375</v>
       </c>
       <c r="I95" t="n">
-        <v>15.61049326574916</v>
+        <v>12.14174102013381</v>
       </c>
       <c r="J95" t="n">
-        <v>1.123286276365474</v>
+        <v>0.9649988515007424</v>
       </c>
       <c r="K95" t="n">
-        <v>1.371244953353325</v>
+        <v>1.345532631520481</v>
       </c>
       <c r="L95" t="n">
-        <v>0.1888724205516809</v>
+        <v>0.1473112422340023</v>
       </c>
       <c r="M95" t="n">
-        <v>0.3675863960404082</v>
+        <v>0.2900723324797689</v>
       </c>
       <c r="N95" t="n">
-        <v>0.4946603075352639</v>
+        <v>0.4518579411433632</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0466253462666364</v>
+        <v>0.0383709078692153</v>
       </c>
     </row>
     <row r="96">
@@ -5690,34 +5690,34 @@
         <v>0.5</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G96" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H96" t="n">
-        <v>34.75</v>
+        <v>34.9375</v>
       </c>
       <c r="I96" t="n">
-        <v>18.63296809421408</v>
+        <v>16.70504695443865</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9854020587485166</v>
+        <v>0.7404427559686634</v>
       </c>
       <c r="K96" t="n">
-        <v>1.183663518806358</v>
+        <v>1.009429234791502</v>
       </c>
       <c r="L96" t="n">
-        <v>0.2660850252826905</v>
+        <v>0.125705720651823</v>
       </c>
       <c r="M96" t="n">
-        <v>0.3106641007702985</v>
+        <v>0.2143859195219638</v>
       </c>
       <c r="N96" t="n">
-        <v>0.4378095864812368</v>
+        <v>0.3587770235382969</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0596523537604069</v>
+        <v>0.0337815841065137</v>
       </c>
     </row>
     <row r="97">
@@ -5745,34 +5745,34 @@
         <v>0.5</v>
       </c>
       <c r="F97" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H97" t="n">
-        <v>53.75</v>
+        <v>50.84615384615385</v>
       </c>
       <c r="I97" t="n">
-        <v>14.8891739193281</v>
+        <v>16.28990321473894</v>
       </c>
       <c r="J97" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="K97" t="n">
-        <v>0.5573254569271926</v>
+        <v>0.5653385818479379</v>
       </c>
       <c r="L97" t="n">
-        <v>0.8891379295116182</v>
+        <v>0.8654224368507433</v>
       </c>
       <c r="M97" t="n">
-        <v>0.1623807660752869</v>
+        <v>0.1504649048763514</v>
       </c>
       <c r="N97" t="n">
-        <v>0.06900520215139951</v>
+        <v>0.07040775724912619</v>
       </c>
       <c r="O97" t="n">
-        <v>0.1448903727100377</v>
+        <v>0.1417572110024848</v>
       </c>
     </row>
   </sheetData>
@@ -5859,10 +5859,10 @@
         <v/>
       </c>
       <c r="G2" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
     </row>
     <row r="3">
@@ -5887,16 +5887,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>47.5</v>
+        <v>47.1304347826087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1819528125953422</v>
+        <v>0.1482805504521079</v>
       </c>
     </row>
     <row r="4">
@@ -5921,16 +5921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
-        <v>34.125</v>
+        <v>45.94444444444444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0478868897788192</v>
+        <v>0.033462798467233</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1275887324970493</v>
+        <v>0.105255345479735</v>
       </c>
     </row>
     <row r="5">
@@ -5955,16 +5955,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40.6595744680851</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001576889925524</v>
+        <v>0.001039217390027</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0100554104722364</v>
+        <v>0.0154768037567931</v>
       </c>
     </row>
     <row r="6">
@@ -5992,13 +5992,13 @@
         <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>33.83333333333334</v>
+        <v>35.02222222222223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003188894368445</v>
+        <v>0.0029001126302991</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0123342490641131</v>
+        <v>0.019283522202299</v>
       </c>
     </row>
     <row r="7">
@@ -6023,16 +6023,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v/>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1467344656676207</v>
+        <v>0.1559023321461803</v>
       </c>
     </row>
     <row r="8">
@@ -6063,10 +6063,10 @@
         <v/>
       </c>
       <c r="G8" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
     </row>
     <row r="9">
@@ -6091,16 +6091,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>45.16666666666666</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1998309745729286</v>
+        <v>0.1621836264902457</v>
       </c>
     </row>
     <row r="10">
@@ -6125,16 +6125,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>43.42857142857143</v>
+        <v>47.23076923076923</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0776696659269543</v>
+        <v>0.0435392673013738</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1715122576387288</v>
+        <v>0.1261698481298532</v>
       </c>
     </row>
     <row r="11">
@@ -6159,16 +6159,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>40.33333333333334</v>
+        <v>40.87878787878788</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001454395450638</v>
+        <v>0.0022785422918566</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0347527523747741</v>
+        <v>0.0417805044648733</v>
       </c>
     </row>
     <row r="12">
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>33.44444444444444</v>
+        <v>36.57575757575758</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0019264161245788</v>
+        <v>0.0015910837231041</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0403912926622152</v>
+        <v>0.0343422322692095</v>
       </c>
     </row>
     <row r="13">
@@ -6227,16 +6227,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v/>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1542279335364008</v>
+        <v>0.1632645918866416</v>
       </c>
     </row>
     <row r="14">
@@ -6267,10 +6267,10 @@
         <v/>
       </c>
       <c r="G14" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
     </row>
     <row r="15">
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F15" t="n">
-        <v>47.5</v>
+        <v>47.1304347826087</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1819528125953422</v>
+        <v>0.1482805504521079</v>
       </c>
     </row>
     <row r="16">
@@ -6329,16 +6329,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1027591027792983</v>
+        <v>0.07026897685516401</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1890853437052657</v>
+        <v>0.1518954126704325</v>
       </c>
     </row>
     <row r="17">
@@ -6363,16 +6363,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>53.125</v>
+        <v>49.64</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0278407789078835</v>
+        <v>0.0244986007715494</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1071950788665455</v>
+        <v>0.0970406891100932</v>
       </c>
     </row>
     <row r="18">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>47.44444444444444</v>
+        <v>43.34782608695652</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0739482796561807</v>
+        <v>0.0653989089806865</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1526880764144908</v>
+        <v>0.1486103911817424</v>
       </c>
     </row>
     <row r="19">
@@ -6431,16 +6431,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v/>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1467344656676207</v>
+        <v>0.1559023321461803</v>
       </c>
     </row>
     <row r="20">
@@ -6471,10 +6471,10 @@
         <v/>
       </c>
       <c r="G20" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5041506705658925</v>
+        <v>0.6377276853746784</v>
       </c>
     </row>
     <row r="21">
@@ -6499,16 +6499,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F21" t="n">
-        <v>45.16666666666666</v>
+        <v>46.47058823529412</v>
       </c>
       <c r="G21" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1998309745729286</v>
+        <v>0.1621836264902457</v>
       </c>
     </row>
     <row r="22">
@@ -6533,16 +6533,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>56.66666666666666</v>
+        <v>50.125</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0945757989443753</v>
+        <v>0.0596004780297778</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2069335216821159</v>
+        <v>0.1561473070809447</v>
       </c>
     </row>
     <row r="23">
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>54.28571428571428</v>
+        <v>49.58823529411764</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0272042912092492</v>
+        <v>0.023288155223405</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1014106099207696</v>
+        <v>0.1034520815299974</v>
       </c>
     </row>
     <row r="24">
@@ -6601,16 +6601,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0647658539144659</v>
+        <v>0.06591725041837081</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1731680580449073</v>
+        <v>0.1711803626946721</v>
       </c>
     </row>
     <row r="25">
@@ -6635,16 +6635,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v/>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1542279335364008</v>
+        <v>0.1632645918866416</v>
       </c>
     </row>
     <row r="26">
@@ -6669,16 +6669,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.845471059700435</v>
       </c>
     </row>
     <row r="27">
@@ -6703,16 +6703,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="H27" t="n">
-        <v>1.444186909187633</v>
+        <v>1.257662594961341</v>
       </c>
     </row>
     <row r="28">
@@ -6737,16 +6737,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v/>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>1.026560398956106</v>
+        <v>0.7843253210412064</v>
       </c>
       <c r="H28" t="n">
-        <v>0.979619593345628</v>
+        <v>0.8966171596061158</v>
       </c>
     </row>
     <row r="29">
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>25.75</v>
+        <v>29.88235294117647</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5430921795874392</v>
+        <v>0.3778103600790315</v>
       </c>
       <c r="H29" t="n">
-        <v>0.751396205677789</v>
+        <v>0.8283534722804042</v>
       </c>
     </row>
     <row r="30">
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
         <v>56</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2209616741970988</v>
+        <v>0.3146572461488882</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7028547522549716</v>
+        <v>0.7820946327252301</v>
       </c>
     </row>
     <row r="31">
@@ -6839,16 +6839,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F31" t="n">
-        <v>45.83333333333334</v>
+        <v>49.64285714285715</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="H31" t="n">
-        <v>0.696020969371498</v>
+        <v>0.7598856465951712</v>
       </c>
     </row>
     <row r="32">
@@ -6873,16 +6873,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.8428334306489031</v>
       </c>
     </row>
     <row r="33">
@@ -6907,16 +6907,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>38.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="H33" t="n">
-        <v>1.501425102377896</v>
+        <v>1.296566442979504</v>
       </c>
     </row>
     <row r="34">
@@ -6941,16 +6941,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v/>
+        <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>1.021366535291565</v>
+        <v>0.8033992323085697</v>
       </c>
       <c r="H34" t="n">
-        <v>1.074975762493408</v>
+        <v>0.9484705495654446</v>
       </c>
     </row>
     <row r="35">
@@ -6975,16 +6975,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F35" t="n">
-        <v>22</v>
+        <v>24.38461538461538</v>
       </c>
       <c r="G35" t="n">
-        <v>0.533727686486196</v>
+        <v>0.4452065294449382</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8094513447340782</v>
+        <v>0.9439445633487472</v>
       </c>
     </row>
     <row r="36">
@@ -7009,16 +7009,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
         <v>60.66666666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2347463748366466</v>
+        <v>0.3072457440634565</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7361035709314633</v>
+        <v>0.7950910799492387</v>
       </c>
     </row>
     <row r="37">
@@ -7043,16 +7043,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>48.91666666666666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7532624842722424</v>
+        <v>0.763797982519849</v>
       </c>
     </row>
     <row r="38">
@@ -7077,16 +7077,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.845471059700435</v>
       </c>
     </row>
     <row r="39">
@@ -7111,16 +7111,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G39" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="H39" t="n">
-        <v>1.444186909187633</v>
+        <v>1.257662594961341</v>
       </c>
     </row>
     <row r="40">
@@ -7145,16 +7145,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v/>
+        <v>28.33333333333333</v>
       </c>
       <c r="G40" t="n">
-        <v>1.949282572616417</v>
+        <v>1.609946685715318</v>
       </c>
       <c r="H40" t="n">
-        <v>1.576745623147889</v>
+        <v>1.417631245983388</v>
       </c>
     </row>
     <row r="41">
@@ -7179,16 +7179,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F41" t="n">
-        <v>35.25</v>
+        <v>39.18181818181818</v>
       </c>
       <c r="G41" t="n">
-        <v>1.563056352530661</v>
+        <v>1.412128529358507</v>
       </c>
       <c r="H41" t="n">
-        <v>1.275320296244268</v>
+        <v>1.214469083767631</v>
       </c>
     </row>
     <row r="42">
@@ -7213,16 +7213,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v/>
+        <v>23</v>
       </c>
       <c r="G42" t="n">
-        <v>1.20123224871285</v>
+        <v>1.079054336554641</v>
       </c>
       <c r="H42" t="n">
-        <v>1.37523996600375</v>
+        <v>1.221459067780741</v>
       </c>
     </row>
     <row r="43">
@@ -7247,16 +7247,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F43" t="n">
-        <v>45.83333333333334</v>
+        <v>49.64285714285715</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="H43" t="n">
-        <v>0.696020969371498</v>
+        <v>0.7598856465951712</v>
       </c>
     </row>
     <row r="44">
@@ -7281,16 +7281,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7928348378302343</v>
+        <v>0.8428334306489031</v>
       </c>
     </row>
     <row r="45">
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>38.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="H45" t="n">
-        <v>1.501425102377896</v>
+        <v>1.296566442979504</v>
       </c>
     </row>
     <row r="46">
@@ -7349,16 +7349,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v/>
+        <v>35.33333333333334</v>
       </c>
       <c r="G46" t="n">
-        <v>2.0573208415366</v>
+        <v>1.688443823970663</v>
       </c>
       <c r="H46" t="n">
-        <v>1.600401412276286</v>
+        <v>1.43749085370591</v>
       </c>
     </row>
     <row r="47">
@@ -7383,16 +7383,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F47" t="n">
-        <v>33.25</v>
+        <v>41</v>
       </c>
       <c r="G47" t="n">
-        <v>1.608821480653673</v>
+        <v>1.411565748608577</v>
       </c>
       <c r="H47" t="n">
-        <v>1.312146048873493</v>
+        <v>1.232008747455892</v>
       </c>
     </row>
     <row r="48">
@@ -7417,16 +7417,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v/>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
-        <v>1.266142192995252</v>
+        <v>1.177559786316756</v>
       </c>
       <c r="H48" t="n">
-        <v>1.405119569320728</v>
+        <v>1.273762223299103</v>
       </c>
     </row>
     <row r="49">
@@ -7451,16 +7451,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>48.91666666666666</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7532624842722424</v>
+        <v>0.763797982519849</v>
       </c>
     </row>
     <row r="50">
@@ -7485,16 +7485,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="H50" t="n">
-        <v>1.317351707463459</v>
+        <v>1.517158043021304</v>
       </c>
     </row>
     <row r="51">
@@ -7519,16 +7519,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>53.16666666666666</v>
+        <v>49.23076923076923</v>
       </c>
       <c r="G51" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="H51" t="n">
-        <v>1.342021237387835</v>
+        <v>1.332412035158513</v>
       </c>
     </row>
     <row r="52">
@@ -7553,16 +7553,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G52" t="n">
-        <v>3.240208371863152</v>
+        <v>3.475260170951214</v>
       </c>
       <c r="H52" t="n">
-        <v>1.140927828707851</v>
+        <v>1.085844437904566</v>
       </c>
     </row>
     <row r="53">
@@ -7587,16 +7587,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G53" t="n">
-        <v>3.432205526950077</v>
+        <v>3.774925420641969</v>
       </c>
       <c r="H53" t="n">
-        <v>1.515523008264331</v>
+        <v>1.59262414495807</v>
       </c>
     </row>
     <row r="54">
@@ -7624,13 +7624,13 @@
         <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="G54" t="n">
-        <v>2.896880552434572</v>
+        <v>2.763048849043291</v>
       </c>
       <c r="H54" t="n">
-        <v>1.073487722064323</v>
+        <v>1.0118316150062</v>
       </c>
     </row>
     <row r="55">
@@ -7655,16 +7655,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>45</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="G55" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="H55" t="n">
-        <v>1.180834807809197</v>
+        <v>1.132387135255874</v>
       </c>
     </row>
     <row r="56">
@@ -7689,16 +7689,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>13</v>
       </c>
       <c r="G56" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="H56" t="n">
-        <v>1.406285393529407</v>
+        <v>1.565050836717096</v>
       </c>
     </row>
     <row r="57">
@@ -7723,16 +7723,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
-        <v>41.75</v>
+        <v>47.08333333333334</v>
       </c>
       <c r="G57" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="H57" t="n">
-        <v>1.284471615179526</v>
+        <v>1.343571408135632</v>
       </c>
     </row>
     <row r="58">
@@ -7757,16 +7757,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>71</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="G58" t="n">
-        <v>3.271126748173042</v>
+        <v>3.295829362112158</v>
       </c>
       <c r="H58" t="n">
-        <v>1.06113533475451</v>
+        <v>1.042008266069966</v>
       </c>
     </row>
     <row r="59">
@@ -7791,16 +7791,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F59" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G59" t="n">
-        <v>3.439709319043941</v>
+        <v>3.998993936933476</v>
       </c>
       <c r="H59" t="n">
-        <v>1.448707858961522</v>
+        <v>1.510129805005717</v>
       </c>
     </row>
     <row r="60">
@@ -7825,16 +7825,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F60" t="n">
-        <v>53.66666666666666</v>
+        <v>56.5</v>
       </c>
       <c r="G60" t="n">
-        <v>3.08532419385823</v>
+        <v>3.29777010421497</v>
       </c>
       <c r="H60" t="n">
-        <v>1.084792191040415</v>
+        <v>1.223461421858214</v>
       </c>
     </row>
     <row r="61">
@@ -7859,16 +7859,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F61" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="G61" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="H61" t="n">
-        <v>1.083896779809906</v>
+        <v>1.089443516269316</v>
       </c>
     </row>
     <row r="62">
@@ -7893,16 +7893,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="H62" t="n">
-        <v>1.317351707463459</v>
+        <v>1.517158043021304</v>
       </c>
     </row>
     <row r="63">
@@ -7927,16 +7927,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
-        <v>53.16666666666666</v>
+        <v>49.23076923076923</v>
       </c>
       <c r="G63" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="H63" t="n">
-        <v>1.342021237387835</v>
+        <v>1.332412035158513</v>
       </c>
     </row>
     <row r="64">
@@ -7961,16 +7961,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F64" t="n">
-        <v>43.14285714285715</v>
+        <v>40.71428571428572</v>
       </c>
       <c r="G64" t="n">
-        <v>2.87457346701875</v>
+        <v>2.74180848964904</v>
       </c>
       <c r="H64" t="n">
-        <v>1.263810768803331</v>
+        <v>1.295593505125749</v>
       </c>
     </row>
     <row r="65">
@@ -7995,16 +7995,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
-        <v>41</v>
+        <v>44.4</v>
       </c>
       <c r="G65" t="n">
-        <v>1.913234301077092</v>
+        <v>2.184474140912512</v>
       </c>
       <c r="H65" t="n">
-        <v>1.159418188992784</v>
+        <v>1.240927668374411</v>
       </c>
     </row>
     <row r="66">
@@ -8029,16 +8029,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v/>
+        <v>44</v>
       </c>
       <c r="G66" t="n">
-        <v>3.552351406613214</v>
+        <v>3.289909449212436</v>
       </c>
       <c r="H66" t="n">
-        <v>1.576992306451476</v>
+        <v>1.49482836036725</v>
       </c>
     </row>
     <row r="67">
@@ -8063,16 +8063,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>45</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="G67" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="H67" t="n">
-        <v>1.180834807809197</v>
+        <v>1.132387135255874</v>
       </c>
     </row>
     <row r="68">
@@ -8097,16 +8097,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>13</v>
       </c>
       <c r="G68" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="H68" t="n">
-        <v>1.406285393529407</v>
+        <v>1.565050836717096</v>
       </c>
     </row>
     <row r="69">
@@ -8131,16 +8131,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>41.75</v>
+        <v>47.08333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="H69" t="n">
-        <v>1.284471615179526</v>
+        <v>1.343571408135632</v>
       </c>
     </row>
     <row r="70">
@@ -8165,16 +8165,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>43.16666666666666</v>
+        <v>39.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.621339418098632</v>
+        <v>3.017672585517013</v>
       </c>
       <c r="H70" t="n">
-        <v>1.218002177386809</v>
+        <v>1.373860453321078</v>
       </c>
     </row>
     <row r="71">
@@ -8199,16 +8199,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F71" t="n">
-        <v>48</v>
+        <v>39.71428571428572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.491488891931755</v>
+        <v>2.217037544021018</v>
       </c>
       <c r="H71" t="n">
-        <v>1.243380091473654</v>
+        <v>1.206463788967818</v>
       </c>
     </row>
     <row r="72">
@@ -8233,16 +8233,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G72" t="n">
-        <v>4.133461220047512</v>
+        <v>3.489242329377287</v>
       </c>
       <c r="H72" t="n">
-        <v>1.712979624080441</v>
+        <v>1.616782849248249</v>
       </c>
     </row>
     <row r="73">
@@ -8267,16 +8267,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="G73" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="H73" t="n">
-        <v>1.083896779809906</v>
+        <v>1.089443516269316</v>
       </c>
     </row>
     <row r="74">
@@ -8301,16 +8301,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>13</v>
       </c>
       <c r="G74" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7459414848044662</v>
       </c>
     </row>
     <row r="75">
@@ -8335,16 +8335,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F75" t="n">
-        <v>42.23076923076923</v>
+        <v>41.12121212121212</v>
       </c>
       <c r="G75" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3322798282634774</v>
+        <v>0.2804080072741859</v>
       </c>
     </row>
     <row r="76">
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>48.5625</v>
+        <v>41.91891891891892</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5244680645286115</v>
+        <v>0.7841264251850864</v>
       </c>
       <c r="H76" t="n">
-        <v>0.156854979541749</v>
+        <v>0.2689669727369452</v>
       </c>
     </row>
     <row r="77">
@@ -8403,16 +8403,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F77" t="n">
-        <v>28.75</v>
+        <v>31.95238095238096</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4342414697038436</v>
+        <v>0.4127514240458644</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1291979132700974</v>
+        <v>0.1330196891303455</v>
       </c>
     </row>
     <row r="78">
@@ -8437,16 +8437,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F78" t="n">
-        <v>34.38888888888889</v>
+        <v>37.06521739130435</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2108504709006535</v>
+        <v>0.229229150615906</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0683618646086024</v>
+        <v>0.07622401556846729</v>
       </c>
     </row>
     <row r="79">
@@ -8471,16 +8471,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
-        <v>50.66666666666666</v>
+        <v>53.66666666666666</v>
       </c>
       <c r="G79" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1685217717513979</v>
+        <v>0.1623611943016591</v>
       </c>
     </row>
     <row r="80">
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
         <v>13</v>
       </c>
       <c r="G80" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7554543100898569</v>
       </c>
     </row>
     <row r="81">
@@ -8539,16 +8539,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F81" t="n">
-        <v>39.35714285714285</v>
+        <v>36.64705882352941</v>
       </c>
       <c r="G81" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="H81" t="n">
-        <v>0.327565001173614</v>
+        <v>0.2956148435667205</v>
       </c>
     </row>
     <row r="82">
@@ -8573,16 +8573,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F82" t="n">
-        <v>42.15384615384615</v>
+        <v>40.6764705882353</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8731825644241763</v>
+        <v>0.8257406734139249</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2381197770737083</v>
+        <v>0.2605197291370963</v>
       </c>
     </row>
     <row r="83">
@@ -8607,16 +8607,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F83" t="n">
-        <v>30.88235294117647</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="G83" t="n">
-        <v>0.268652913319751</v>
+        <v>0.3117104398512642</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0784704539736349</v>
+        <v>0.09047272338471481</v>
       </c>
     </row>
     <row r="84">
@@ -8641,16 +8641,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F84" t="n">
-        <v>35.52941176470588</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5710505853853267</v>
+        <v>0.5480811890201259</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2169922033723937</v>
+        <v>0.1859561005550112</v>
       </c>
     </row>
     <row r="85">
@@ -8675,16 +8675,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F85" t="n">
-        <v>53.75</v>
+        <v>50.84615384615385</v>
       </c>
       <c r="G85" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1623807660752869</v>
+        <v>0.1504649048763514</v>
       </c>
     </row>
     <row r="86">
@@ -8709,16 +8709,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>13</v>
       </c>
       <c r="G86" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="H86" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7459414848044662</v>
       </c>
     </row>
     <row r="87">
@@ -8743,16 +8743,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F87" t="n">
-        <v>42.23076923076923</v>
+        <v>41.12121212121212</v>
       </c>
       <c r="G87" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3322798282634774</v>
+        <v>0.2804080072741859</v>
       </c>
     </row>
     <row r="88">
@@ -8777,16 +8777,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>36.25</v>
+        <v>34.88461538461539</v>
       </c>
       <c r="G88" t="n">
-        <v>1.111669912723853</v>
+        <v>1.342777348916411</v>
       </c>
       <c r="H88" t="n">
-        <v>0.3601819609140434</v>
+        <v>0.4730463666638156</v>
       </c>
     </row>
     <row r="89">
@@ -8811,16 +8811,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F89" t="n">
-        <v>35.25</v>
+        <v>34.2258064516129</v>
       </c>
       <c r="G89" t="n">
-        <v>1.082900978758997</v>
+        <v>1.010267106779598</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3625516561642117</v>
+        <v>0.3141753362436059</v>
       </c>
     </row>
     <row r="90">
@@ -8845,16 +8845,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F90" t="n">
-        <v>33.66666666666666</v>
+        <v>37.75757575757576</v>
       </c>
       <c r="G90" t="n">
-        <v>1.052165108906756</v>
+        <v>0.901472723746057</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3389114149749481</v>
+        <v>0.2781181955099485</v>
       </c>
     </row>
     <row r="91">
@@ -8879,16 +8879,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
-        <v>50.66666666666666</v>
+        <v>53.66666666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1685217717513979</v>
+        <v>0.1623611943016591</v>
       </c>
     </row>
     <row r="92">
@@ -8913,16 +8913,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>13</v>
       </c>
       <c r="G92" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5620551819181088</v>
+        <v>0.7554543100898569</v>
       </c>
     </row>
     <row r="93">
@@ -8947,16 +8947,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F93" t="n">
-        <v>39.35714285714285</v>
+        <v>36.64705882352941</v>
       </c>
       <c r="G93" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="H93" t="n">
-        <v>0.327565001173614</v>
+        <v>0.2956148435667205</v>
       </c>
     </row>
     <row r="94">
@@ -8981,16 +8981,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F94" t="n">
-        <v>38.4</v>
+        <v>39.55882352941177</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9382823360174214</v>
+        <v>0.9858360467114322</v>
       </c>
       <c r="H94" t="n">
-        <v>0.342977740623145</v>
+        <v>0.3511914870750401</v>
       </c>
     </row>
     <row r="95">
@@ -9015,16 +9015,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F95" t="n">
-        <v>33.75</v>
+        <v>33.375</v>
       </c>
       <c r="G95" t="n">
-        <v>1.123286276365474</v>
+        <v>0.9649988515007424</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3675863960404082</v>
+        <v>0.2900723324797689</v>
       </c>
     </row>
     <row r="96">
@@ -9049,16 +9049,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F96" t="n">
-        <v>34.75</v>
+        <v>34.9375</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9854020587485166</v>
+        <v>0.7404427559686634</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3106641007702985</v>
+        <v>0.2143859195219638</v>
       </c>
     </row>
     <row r="97">
@@ -9083,16 +9083,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F97" t="n">
-        <v>53.75</v>
+        <v>50.84615384615385</v>
       </c>
       <c r="G97" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1623807660752869</v>
+        <v>0.1504649048763514</v>
       </c>
     </row>
   </sheetData>
@@ -9183,22 +9183,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F2" t="n">
-        <v>1.111669912723853</v>
+        <v>1.342777348916411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0908933073142781</v>
+        <v>0.4636784008790098</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J2" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -9223,22 +9223,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F3" t="n">
-        <v>1.082900978758997</v>
+        <v>1.010267106779598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0621243733494216</v>
+        <v>0.1311681587421966</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -9263,22 +9263,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F4" t="n">
-        <v>1.052165108906756</v>
+        <v>0.901472723746057</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0313885034971814</v>
+        <v>0.0223737757086556</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -9303,22 +9303,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F5" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0981169912886363</v>
+        <v>0.1103519081976235</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -9343,22 +9343,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="G6" t="n">
-        <v>1.656590233866588</v>
+        <v>2.155016649139553</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -9383,22 +9383,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9382823360174214</v>
+        <v>0.9858360467114322</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0061076691127585</v>
+        <v>0.0911371271241779</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J7" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -9423,22 +9423,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F8" t="n">
-        <v>1.123286276365474</v>
+        <v>0.9649988515007424</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1788962712352937</v>
+        <v>0.0702999319134882</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -9463,22 +9463,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9854020587485166</v>
+        <v>0.7404427559686634</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0410120536183367</v>
+        <v>-0.1542561636185908</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J9" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -9503,22 +9503,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F10" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1054803006318956</v>
+        <v>0.0659637565324994</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -9543,22 +9543,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F11" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="G11" t="n">
-        <v>1.732976834145984</v>
+        <v>2.14046945247077</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -9583,22 +9583,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5244680645286115</v>
+        <v>0.7841264251850864</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4963085408809635</v>
+        <v>-0.094972522852315</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J12" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -9623,22 +9623,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4342414697038436</v>
+        <v>0.4127514240458644</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5865351357057315</v>
+        <v>-0.466347523991537</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -9663,22 +9663,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2108504709006535</v>
+        <v>0.229229150615906</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8099261345089215</v>
+        <v>-0.6498697974214954</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -9703,22 +9703,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F15" t="n">
-        <v>1.118893596698211</v>
+        <v>0.9894508562350248</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0981169912886363</v>
+        <v>0.1103519081976235</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -9743,22 +9743,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.020776605409575</v>
+        <v>0.8790989480374014</v>
       </c>
       <c r="F16" t="n">
-        <v>2.677366839276164</v>
+        <v>3.034115597176954</v>
       </c>
       <c r="G16" t="n">
-        <v>1.656590233866588</v>
+        <v>2.155016649139553</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -9783,22 +9783,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8731825644241763</v>
+        <v>0.8257406734139249</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0712074407060036</v>
+        <v>-0.0689582461733293</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J17" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -9823,22 +9823,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.268652913319751</v>
+        <v>0.3117104398512642</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6757370918104288</v>
+        <v>-0.5829884797359901</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J18" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -9863,22 +9863,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5710505853853267</v>
+        <v>0.5480811890201259</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3733394197448532</v>
+        <v>-0.3466177305671283</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J19" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -9903,22 +9903,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F20" t="n">
-        <v>1.049870305762076</v>
+        <v>0.9606626761197536</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1054803006318956</v>
+        <v>0.0659637565324994</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -9943,22 +9943,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.94439000513018</v>
+        <v>0.8946989195872542</v>
       </c>
       <c r="F21" t="n">
-        <v>2.677366839276164</v>
+        <v>3.035168372058024</v>
       </c>
       <c r="G21" t="n">
-        <v>1.732976834145984</v>
+        <v>2.14046945247077</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -9983,22 +9983,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F22" t="n">
-        <v>2.87457346701875</v>
+        <v>2.74180848964904</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5044682686348052</v>
+        <v>0.2215264191156918</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -10023,22 +10023,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F23" t="n">
-        <v>1.913234301077092</v>
+        <v>2.184474140912512</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4568708973068525</v>
+        <v>-0.3358079296208367</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -10063,22 +10063,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F24" t="n">
-        <v>3.552351406613214</v>
+        <v>3.289909449212436</v>
       </c>
       <c r="G24" t="n">
-        <v>1.182246208229269</v>
+        <v>0.7696273786790879</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -10103,22 +10103,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F25" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="G25" t="n">
-        <v>0.522739690387557</v>
+        <v>0.4584522163888702</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -10143,22 +10143,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F26" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="G26" t="n">
-        <v>3.662168707796183</v>
+        <v>3.582977199601632</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -10183,22 +10183,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F27" t="n">
-        <v>2.621339418098632</v>
+        <v>3.017672585517013</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1435659046241824</v>
+        <v>0.1708539217697602</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -10223,22 +10223,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F28" t="n">
-        <v>2.491488891931755</v>
+        <v>2.217037544021018</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0137153784573058</v>
+        <v>-0.6297811197262342</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F29" t="n">
-        <v>4.133461220047512</v>
+        <v>3.489242329377287</v>
       </c>
       <c r="G29" t="n">
-        <v>1.655687706573063</v>
+        <v>0.6424236656300342</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -10303,22 +10303,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F30" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0858500359890905</v>
+        <v>0.057779390267906</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -10343,22 +10343,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F31" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="G31" t="n">
-        <v>3.562577986080735</v>
+        <v>3.265516437665364</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -10383,22 +10383,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F32" t="n">
-        <v>3.240208371863152</v>
+        <v>3.475260170951214</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8701031734792068</v>
+        <v>0.9549781004178656</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -10423,22 +10423,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F33" t="n">
-        <v>3.432205526950077</v>
+        <v>3.774925420641969</v>
       </c>
       <c r="G33" t="n">
-        <v>1.062100328566132</v>
+        <v>1.254643350108621</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -10463,19 +10463,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F34" t="n">
-        <v>2.896880552434572</v>
+        <v>2.763048849043291</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5267753540506264</v>
+        <v>0.2427667785099423</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
         <v>10</v>
@@ -10503,22 +10503,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F35" t="n">
-        <v>2.892844888771502</v>
+        <v>2.978734286922218</v>
       </c>
       <c r="G35" t="n">
-        <v>0.522739690387557</v>
+        <v>0.4584522163888702</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -10543,22 +10543,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.370105198383945</v>
+        <v>2.520282070533348</v>
       </c>
       <c r="F36" t="n">
-        <v>6.032273906180128</v>
+        <v>6.103259270134981</v>
       </c>
       <c r="G36" t="n">
-        <v>3.662168707796183</v>
+        <v>3.582977199601632</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -10583,22 +10583,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F37" t="n">
-        <v>3.271126748173042</v>
+        <v>3.295829362112158</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7933532346985928</v>
+        <v>0.4490106983649058</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -10623,22 +10623,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F38" t="n">
-        <v>3.439709319043941</v>
+        <v>3.998993936933476</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9619358055694912</v>
+        <v>1.152175273186223</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -10663,22 +10663,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F39" t="n">
-        <v>3.08532419385823</v>
+        <v>3.29777010421497</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6075506803837802</v>
+        <v>0.4509514404677173</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -10703,22 +10703,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F40" t="n">
-        <v>2.56362354946354</v>
+        <v>2.904598054015159</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0858500359890905</v>
+        <v>0.057779390267906</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -10743,22 +10743,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2.47777351347445</v>
+        <v>2.846818663747253</v>
       </c>
       <c r="F41" t="n">
-        <v>6.040351499555185</v>
+        <v>6.112335101412617</v>
       </c>
       <c r="G41" t="n">
-        <v>3.562577986080735</v>
+        <v>3.265516437665364</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -10783,22 +10783,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F42" t="n">
-        <v>1.949282572616417</v>
+        <v>1.609946685715318</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0474491197949533</v>
+        <v>0.1859042972254097</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -10823,22 +10823,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F43" t="n">
-        <v>1.563056352530661</v>
+        <v>1.412128529358507</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.338777100290802</v>
+        <v>-0.0119138591314005</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J43" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -10863,22 +10863,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F44" t="n">
-        <v>1.20123224871285</v>
+        <v>1.079054336554641</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.7006012041086138</v>
+        <v>-0.3449880519352668</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -10903,22 +10903,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.69739265053509</v>
+        <v>-0.9947777835849538</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J45" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -10943,22 +10943,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.139618656347493</v>
+        <v>-0.584909713227444</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" t="n">
         <v>10</v>
-      </c>
-      <c r="J46" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -10983,22 +10983,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0573208415366</v>
+        <v>1.688443823970663</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0549989636467405</v>
+        <v>0.2175759574213085</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -11023,22 +11023,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F48" t="n">
-        <v>1.608821480653673</v>
+        <v>1.411565748608577</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.3935003972361863</v>
+        <v>-0.0593021179407768</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -11063,22 +11063,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F49" t="n">
-        <v>1.266142192995252</v>
+        <v>1.177559786316756</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7361796848946076</v>
+        <v>-0.2933080802325982</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -11103,22 +11103,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.766414485490487</v>
+        <v>-1.018324452865149</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -11143,22 +11143,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.24010708141589</v>
+        <v>-0.6301241471390183</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -11183,22 +11183,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F52" t="n">
-        <v>1.026560398956106</v>
+        <v>0.7843253210412064</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.8752730538653573</v>
+        <v>-0.6397170674487014</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -11223,22 +11223,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5430921795874392</v>
+        <v>0.3778103600790315</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.358741273234024</v>
+        <v>-1.046232028410876</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
@@ -11263,22 +11263,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2209616741970988</v>
+        <v>0.3146572461488882</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.680871778624364</v>
+        <v>-1.10938514234102</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -11303,22 +11303,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2044408022863736</v>
+        <v>0.429264604904954</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.69739265053509</v>
+        <v>-0.9947777835849538</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -11343,22 +11343,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.901833452821464</v>
+        <v>1.424042388489908</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8391326752624638</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.139618656347493</v>
+        <v>-0.584909713227444</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
       </c>
       <c r="I56" t="n">
+        <v>12</v>
+      </c>
+      <c r="J56" t="n">
         <v>10</v>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -11383,22 +11383,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F57" t="n">
-        <v>1.021366535291565</v>
+        <v>0.8033992323085697</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9809553425982948</v>
+        <v>-0.6674686342407843</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -11423,22 +11423,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F58" t="n">
-        <v>0.533727686486196</v>
+        <v>0.4452065294449382</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.468594191403664</v>
+        <v>-1.025661337104416</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J58" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
@@ -11463,22 +11463,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2347463748366466</v>
+        <v>0.3072457440634565</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.767575503053213</v>
+        <v>-1.163622122485897</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J59" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -11503,22 +11503,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2359073923993729</v>
+        <v>0.4525434136842047</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.766414485490487</v>
+        <v>-1.018324452865149</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -11543,22 +11543,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2.00232187788986</v>
+        <v>1.470867866549354</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7622147964739701</v>
+        <v>0.8407437194103357</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.24010708141589</v>
+        <v>-0.6301241471390183</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -11583,22 +11583,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1027591027792983</v>
+        <v>0.07026897685516401</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.0088015780440765</v>
+        <v>0.0009021190904057</v>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J62" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -11623,22 +11623,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0278407789078835</v>
+        <v>0.0244986007715494</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.08371990191549129</v>
+        <v>-0.0448682569932088</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J63" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
@@ -11663,22 +11663,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0739482796561807</v>
+        <v>0.0653989089806865</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.0376124011671941</v>
+        <v>-0.0039679487840718</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J64" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65">
@@ -11703,22 +11703,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.08672537741979409</v>
+        <v>-0.0370006860656634</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -11743,19 +11743,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F66" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2356134965464952</v>
+        <v>0.4570302594577225</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -11783,22 +11783,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0945757989443753</v>
+        <v>0.0596004780297778</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0147670683124796</v>
+        <v>-0.0052894577201624</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J67" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
@@ -11823,22 +11823,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0272042912092492</v>
+        <v>0.023288155223405</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.0821385760476057</v>
+        <v>-0.0416017805265352</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J68" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
@@ -11863,22 +11863,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0647658539144659</v>
+        <v>0.06591725041837081</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.044577013342389</v>
+        <v>0.0010273146684305</v>
       </c>
       <c r="H69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J69" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -11903,22 +11903,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.0821763976382035</v>
+        <v>-0.0289523756690603</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -11943,19 +11943,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F71" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="G71" t="n">
-        <v>0.237831310113015</v>
+        <v>0.4615071814725405</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -11983,22 +11983,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0478868897788192</v>
+        <v>0.033462798467233</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.06367379104455551</v>
+        <v>-0.0359040592975253</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J72" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
@@ -12023,22 +12023,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0001576889925524</v>
+        <v>0.001039217390027</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.1114029918308223</v>
+        <v>-0.0683276403747312</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J73" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
@@ -12063,19 +12063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0003188894368445</v>
+        <v>0.0029001126302991</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.1112417913865302</v>
+        <v>-0.0664667451344591</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J74" t="n">
         <v>90</v>
@@ -12103,22 +12103,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0248353034035807</v>
+        <v>0.0323661716990949</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.08672537741979409</v>
+        <v>-0.0370006860656634</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.1115606808233748</v>
+        <v>0.0693668577647583</v>
       </c>
       <c r="F76" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2356134965464952</v>
+        <v>0.4570302594577225</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -12183,22 +12183,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0776696659269543</v>
+        <v>0.0435392673013738</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0316732013299006</v>
+        <v>-0.0213506684485665</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J77" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -12223,22 +12223,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F78" t="n">
-        <v>0.001454395450638</v>
+        <v>0.0022785422918566</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.1078884718062169</v>
+        <v>-0.0626113934580836</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J78" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
@@ -12263,22 +12263,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0019264161245788</v>
+        <v>0.0015910837231041</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.1074164511322761</v>
+        <v>-0.0632988520268362</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J79" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80">
@@ -12303,22 +12303,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0271664696186514</v>
+        <v>0.03593756008088</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.0821763976382035</v>
+        <v>-0.0289523756690603</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -12343,19 +12343,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.109342867256855</v>
+        <v>0.0648899357499403</v>
       </c>
       <c r="F81" t="n">
-        <v>0.34717417736987</v>
+        <v>0.5263971172224808</v>
       </c>
       <c r="G81" t="n">
-        <v>0.237831310113015</v>
+        <v>0.4615071814725405</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
